--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -1645,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124126865</v>
+        <v>124138432</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,42 +1661,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436624</v>
+        <v>436583</v>
       </c>
       <c r="R10" t="n">
-        <v>7027776</v>
+        <v>7028008</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,21 +1718,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1746,51 +1731,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138432</v>
+        <v>124130607</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,37 +1763,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436583</v>
+        <v>436700</v>
       </c>
       <c r="R11" t="n">
-        <v>7028008</v>
+        <v>7027918</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1860,11 +1820,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1873,26 +1843,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124130607</v>
+        <v>124130043</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,41 +1896,60 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436700</v>
+        <v>436564</v>
       </c>
       <c r="R12" t="n">
-        <v>7027918</v>
+        <v>7027844</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1988,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,26 +2003,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2026,10 +2020,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124130043</v>
+        <v>124129722</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,60 +2032,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436564</v>
+        <v>436509</v>
       </c>
       <c r="R13" t="n">
-        <v>7027844</v>
+        <v>7027814</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2120,7 +2095,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2130,7 +2105,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2145,6 +2120,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2162,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124129722</v>
+        <v>124133665</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,20 +2169,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2196,19 +2191,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436509</v>
+        <v>436624</v>
       </c>
       <c r="R14" t="n">
-        <v>7027814</v>
+        <v>7027776</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2247,7 +2247,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,22 +2271,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2299,10 +2304,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124133665</v>
+        <v>124130826</v>
       </c>
       <c r="B15" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2311,31 +2316,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2344,13 +2349,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436624</v>
+        <v>436743</v>
       </c>
       <c r="R15" t="n">
-        <v>7027776</v>
+        <v>7027889</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2379,7 +2384,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2389,12 +2394,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124130826</v>
+        <v>124126979</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2462,27 +2462,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436743</v>
+        <v>436580</v>
       </c>
       <c r="R16" t="n">
-        <v>7027889</v>
+        <v>7027758</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2536,7 +2536,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2565,12 +2570,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2588,10 +2593,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124126979</v>
+        <v>124138452</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>90940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2604,42 +2609,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436580</v>
+        <v>436732</v>
       </c>
       <c r="R17" t="n">
-        <v>7027758</v>
+        <v>7028026</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2666,26 +2666,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2694,51 +2679,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138452</v>
+        <v>124130109</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2751,37 +2711,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436732</v>
+        <v>436613</v>
       </c>
       <c r="R18" t="n">
-        <v>7028026</v>
+        <v>7027858</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2808,11 +2778,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2821,26 +2806,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124130109</v>
+        <v>124138431</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2853,47 +2863,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436613</v>
+        <v>436653</v>
       </c>
       <c r="R19" t="n">
-        <v>7027858</v>
+        <v>7028028</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2920,26 +2920,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2948,51 +2933,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124133343</v>
+        <v>124129449</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3005,42 +2965,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436623</v>
+        <v>436417</v>
       </c>
       <c r="R20" t="n">
-        <v>7027816</v>
+        <v>7027793</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3069,7 +3024,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3079,12 +3034,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3103,22 +3053,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3136,10 +3086,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138431</v>
+        <v>124133629</v>
       </c>
       <c r="B21" t="n">
-        <v>90990</v>
+        <v>79869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3152,37 +3102,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436653</v>
+        <v>436623</v>
       </c>
       <c r="R21" t="n">
-        <v>7028028</v>
+        <v>7027760</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3209,11 +3164,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3222,16 +3192,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Dead branch  # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3345,10 +3340,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124129449</v>
+        <v>124129618</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3361,37 +3356,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436417</v>
+        <v>436474</v>
       </c>
       <c r="R23" t="n">
-        <v>7027793</v>
+        <v>7027820</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3449,22 +3449,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124133629</v>
+        <v>124138453</v>
       </c>
       <c r="B24" t="n">
-        <v>79869</v>
+        <v>91683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3494,46 +3494,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436623</v>
+        <v>436490</v>
       </c>
       <c r="R24" t="n">
-        <v>7027760</v>
+        <v>7027974</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3560,26 +3555,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3588,51 +3568,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124129618</v>
+        <v>124138481</v>
       </c>
       <c r="B25" t="n">
-        <v>79869</v>
+        <v>88337</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3645,42 +3600,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436474</v>
+        <v>436391</v>
       </c>
       <c r="R25" t="n">
-        <v>7027820</v>
+        <v>7027787</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3707,21 +3657,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3730,51 +3670,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138453</v>
+        <v>124138466</v>
       </c>
       <c r="B26" t="n">
-        <v>91683</v>
+        <v>91004</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3783,25 +3698,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3811,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436490</v>
+        <v>436589</v>
       </c>
       <c r="R26" t="n">
-        <v>7027974</v>
+        <v>7027985</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3873,10 +3788,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138481</v>
+        <v>124132562</v>
       </c>
       <c r="B27" t="n">
-        <v>88337</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3889,37 +3804,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436391</v>
+        <v>436679</v>
       </c>
       <c r="R27" t="n">
-        <v>7027787</v>
+        <v>7027841</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3946,11 +3861,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3959,26 +3889,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124132562</v>
+        <v>124134174</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3987,41 +3942,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436679</v>
+        <v>436557</v>
       </c>
       <c r="R28" t="n">
-        <v>7027841</v>
+        <v>7027773</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4050,7 +4010,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4060,12 +4020,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4084,22 +4039,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4117,10 +4072,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124134174</v>
+        <v>124131523</v>
       </c>
       <c r="B29" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4129,46 +4084,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436557</v>
+        <v>436749</v>
       </c>
       <c r="R29" t="n">
-        <v>7027773</v>
+        <v>7027816</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4197,7 +4147,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4207,7 +4157,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4226,22 +4176,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4259,10 +4209,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124131523</v>
+        <v>124131669</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4275,34 +4225,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436749</v>
+        <v>436701</v>
       </c>
       <c r="R30" t="n">
-        <v>7027816</v>
+        <v>7027783</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4334,7 +4289,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4344,7 +4299,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4363,22 +4318,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4396,10 +4351,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138466</v>
+        <v>124126749</v>
       </c>
       <c r="B31" t="n">
-        <v>91004</v>
+        <v>57644</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4412,37 +4367,51 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436589</v>
+        <v>436643</v>
       </c>
       <c r="R31" t="n">
-        <v>7027985</v>
+        <v>7027739</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4469,11 +4438,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4482,26 +4466,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124131669</v>
+        <v>124138476</v>
       </c>
       <c r="B32" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4514,42 +4503,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436701</v>
+        <v>436556</v>
       </c>
       <c r="R32" t="n">
-        <v>7027783</v>
+        <v>7027990</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4576,21 +4560,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4599,51 +4573,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124126749</v>
+        <v>124131819</v>
       </c>
       <c r="B33" t="n">
-        <v>57644</v>
+        <v>79869</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4656,36 +4605,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4694,13 +4634,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436643</v>
+        <v>436725</v>
       </c>
       <c r="R33" t="n">
-        <v>7027739</v>
+        <v>7027833</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4729,7 +4669,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4739,12 +4679,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4759,6 +4694,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4776,10 +4731,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138476</v>
+        <v>124138426</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>90990</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4792,21 +4747,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4816,10 +4771,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436556</v>
+        <v>436760</v>
       </c>
       <c r="R34" t="n">
-        <v>7027990</v>
+        <v>7028081</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4878,10 +4833,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124132300</v>
+        <v>124134617</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4890,55 +4845,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436689</v>
+        <v>436450</v>
       </c>
       <c r="R35" t="n">
-        <v>7027839</v>
+        <v>7027766</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4967,7 +4908,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4977,12 +4918,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4997,6 +4938,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5014,10 +4975,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124131819</v>
+        <v>124131109</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5030,39 +4991,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436725</v>
+        <v>436775</v>
       </c>
       <c r="R36" t="n">
-        <v>7027833</v>
+        <v>7027895</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -5094,7 +5050,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5104,7 +5060,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5123,22 +5079,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5156,10 +5112,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138426</v>
+        <v>124133243</v>
       </c>
       <c r="B37" t="n">
-        <v>90990</v>
+        <v>79898</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5168,41 +5124,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436760</v>
+        <v>436634</v>
       </c>
       <c r="R37" t="n">
-        <v>7028081</v>
+        <v>7027830</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5229,11 +5190,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5242,26 +5213,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124131109</v>
+        <v>124138434</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5274,37 +5270,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436775</v>
+        <v>436588</v>
       </c>
       <c r="R38" t="n">
-        <v>7027895</v>
+        <v>7027994</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5331,21 +5327,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5354,51 +5340,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124134617</v>
+        <v>124134147</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5411,34 +5372,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436450</v>
+        <v>436555</v>
       </c>
       <c r="R39" t="n">
-        <v>7027766</v>
+        <v>7027775</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5470,7 +5436,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5480,12 +5446,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5504,22 +5465,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5537,10 +5498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124133243</v>
+        <v>124138459</v>
       </c>
       <c r="B40" t="n">
-        <v>79898</v>
+        <v>57507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5549,46 +5510,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436634</v>
+        <v>436448</v>
       </c>
       <c r="R40" t="n">
-        <v>7027830</v>
+        <v>7027953</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5615,19 +5571,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:43</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5638,51 +5589,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138434</v>
+        <v>124134307</v>
       </c>
       <c r="B41" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5695,37 +5621,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436588</v>
+        <v>436504</v>
       </c>
       <c r="R41" t="n">
-        <v>7027994</v>
+        <v>7027727</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5752,11 +5678,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5765,26 +5701,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124134147</v>
+        <v>124138436</v>
       </c>
       <c r="B42" t="n">
-        <v>79870</v>
+        <v>90990</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5797,39 +5758,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436555</v>
+        <v>436408</v>
       </c>
       <c r="R42" t="n">
-        <v>7027775</v>
+        <v>7027885</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5859,21 +5815,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5882,51 +5828,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138459</v>
+        <v>124130731</v>
       </c>
       <c r="B43" t="n">
-        <v>57507</v>
+        <v>56692</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5939,16 +5860,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5956,17 +5877,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436448</v>
+        <v>436707</v>
       </c>
       <c r="R43" t="n">
-        <v>7027953</v>
+        <v>7027946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5996,14 +5931,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6014,26 +5954,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124133039</v>
+        <v>124130402</v>
       </c>
       <c r="B44" t="n">
-        <v>90990</v>
+        <v>79905</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6042,31 +5987,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6075,13 +6020,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436650</v>
+        <v>436671</v>
       </c>
       <c r="R44" t="n">
-        <v>7027809</v>
+        <v>7027849</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6110,7 +6055,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6120,7 +6065,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6139,22 +6084,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6172,10 +6117,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124130402</v>
+        <v>124127075</v>
       </c>
       <c r="B45" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6184,25 +6129,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6213,17 +6158,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436671</v>
+        <v>436458</v>
       </c>
       <c r="R45" t="n">
-        <v>7027849</v>
+        <v>7027708</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6252,7 +6197,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6262,7 +6207,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6281,22 +6226,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6314,10 +6259,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124134307</v>
+        <v>124138428</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6330,37 +6275,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436504</v>
+        <v>436678</v>
       </c>
       <c r="R46" t="n">
-        <v>7027727</v>
+        <v>7028031</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6387,21 +6332,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6410,51 +6345,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138436</v>
+        <v>124138462</v>
       </c>
       <c r="B47" t="n">
-        <v>90990</v>
+        <v>91435</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6463,25 +6373,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6491,10 +6401,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436408</v>
+        <v>436591</v>
       </c>
       <c r="R47" t="n">
-        <v>7027885</v>
+        <v>7028013</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6553,10 +6463,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124130731</v>
+        <v>124133343</v>
       </c>
       <c r="B48" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6569,36 +6479,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6607,13 +6508,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436707</v>
+        <v>436623</v>
       </c>
       <c r="R48" t="n">
-        <v>7027946</v>
+        <v>7027816</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6642,7 +6543,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6652,7 +6553,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6667,6 +6573,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6684,10 +6610,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124127075</v>
+        <v>124133039</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6700,42 +6626,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436458</v>
+        <v>436650</v>
       </c>
       <c r="R49" t="n">
-        <v>7027708</v>
+        <v>7027809</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6764,7 +6690,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6774,7 +6700,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6803,12 +6729,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6826,10 +6752,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138428</v>
+        <v>124126865</v>
       </c>
       <c r="B50" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6842,37 +6768,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436678</v>
+        <v>436624</v>
       </c>
       <c r="R50" t="n">
-        <v>7028031</v>
+        <v>7027776</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6899,11 +6830,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6912,26 +6853,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138462</v>
+        <v>124132300</v>
       </c>
       <c r="B51" t="n">
-        <v>91435</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6944,37 +6910,51 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436591</v>
+        <v>436689</v>
       </c>
       <c r="R51" t="n">
-        <v>7028013</v>
+        <v>7027839</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7001,11 +6981,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -7014,16 +7009,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124133534</v>
+        <v>124138436</v>
       </c>
       <c r="B2" t="n">
-        <v>79870</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436627</v>
+        <v>436408</v>
       </c>
       <c r="R2" t="n">
-        <v>7027780</v>
+        <v>7027885</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,26 +748,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138478</v>
+        <v>124134565</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436440</v>
+        <v>436416</v>
       </c>
       <c r="R3" t="n">
-        <v>7027952</v>
+        <v>7027743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,11 +855,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,26 +883,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138474</v>
+        <v>124130109</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,37 +940,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436493</v>
+        <v>436613</v>
       </c>
       <c r="R4" t="n">
-        <v>7027911</v>
+        <v>7027858</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,11 +1007,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,26 +1035,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124130487</v>
+        <v>124134307</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,60 +1088,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436684</v>
+        <v>436504</v>
       </c>
       <c r="R5" t="n">
-        <v>7027902</v>
+        <v>7027727</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1151,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1161,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1176,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1213,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124134565</v>
+        <v>124133243</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,46 +1225,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436416</v>
+        <v>436634</v>
       </c>
       <c r="R6" t="n">
-        <v>7027743</v>
+        <v>7027830</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1293,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1303,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,22 +1322,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,10 +1355,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138425</v>
+        <v>124138462</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,25 +1367,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1344,10 +1395,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436739</v>
+        <v>436591</v>
       </c>
       <c r="R7" t="n">
-        <v>7028034</v>
+        <v>7028013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138423</v>
+        <v>124133665</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>79904</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,41 +1469,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436415</v>
+        <v>436624</v>
       </c>
       <c r="R8" t="n">
-        <v>7027827</v>
+        <v>7027776</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,11 +1535,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1492,26 +1563,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124129992</v>
+        <v>124126979</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,24 +1620,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
@@ -1551,10 +1652,10 @@
         <v>436580</v>
       </c>
       <c r="R9" t="n">
-        <v>7027853</v>
+        <v>7027758</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1694,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,12 +1728,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1645,10 +1751,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124138432</v>
+        <v>124138481</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>88337</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,21 +1767,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1685,10 +1791,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436583</v>
+        <v>436391</v>
       </c>
       <c r="R10" t="n">
-        <v>7028008</v>
+        <v>7027787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,7 +1853,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124130607</v>
+        <v>124132562</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1787,13 +1893,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436700</v>
+        <v>436679</v>
       </c>
       <c r="R11" t="n">
-        <v>7027918</v>
+        <v>7027841</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,7 +1928,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1938,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,10 +1995,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124130043</v>
+        <v>124138478</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,60 +2007,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436564</v>
+        <v>436440</v>
       </c>
       <c r="R12" t="n">
-        <v>7027844</v>
+        <v>7027952</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,21 +2068,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1999,31 +2081,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124129722</v>
+        <v>124130826</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,37 +2113,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436509</v>
+        <v>436743</v>
       </c>
       <c r="R13" t="n">
-        <v>7027814</v>
+        <v>7027889</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2095,7 +2177,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2105,7 +2187,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,12 +2216,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2157,10 +2239,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124133665</v>
+        <v>124129449</v>
       </c>
       <c r="B14" t="n">
-        <v>79904</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,20 +2251,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2191,24 +2273,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436624</v>
+        <v>436417</v>
       </c>
       <c r="R14" t="n">
-        <v>7027776</v>
+        <v>7027793</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2237,7 +2314,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2247,12 +2324,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,22 +2343,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2304,10 +2376,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124130826</v>
+        <v>124133629</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2320,27 +2392,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2349,13 +2421,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436743</v>
+        <v>436623</v>
       </c>
       <c r="R15" t="n">
-        <v>7027889</v>
+        <v>7027760</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,7 +2456,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2394,7 +2466,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2413,22 +2490,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2446,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124126979</v>
+        <v>124129992</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2462,29 +2539,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
@@ -2494,10 +2566,10 @@
         <v>436580</v>
       </c>
       <c r="R16" t="n">
-        <v>7027758</v>
+        <v>7027853</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2526,7 +2598,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2536,12 +2608,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2570,12 +2637,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2593,10 +2660,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138452</v>
+        <v>124129722</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2609,37 +2676,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436732</v>
+        <v>436509</v>
       </c>
       <c r="R17" t="n">
-        <v>7028026</v>
+        <v>7027814</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2666,11 +2733,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2679,23 +2756,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124130109</v>
+        <v>124138459</v>
       </c>
       <c r="B18" t="n">
         <v>57507</v>
@@ -2729,29 +2831,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436613</v>
+        <v>436448</v>
       </c>
       <c r="R18" t="n">
-        <v>7027858</v>
+        <v>7027953</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2778,24 +2870,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2806,48 +2888,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138431</v>
+        <v>124138423</v>
       </c>
       <c r="B19" t="n">
         <v>90990</v>
@@ -2887,10 +2944,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436653</v>
+        <v>436415</v>
       </c>
       <c r="R19" t="n">
-        <v>7028028</v>
+        <v>7027827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2949,10 +3006,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124129449</v>
+        <v>124138425</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2965,34 +3022,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436417</v>
+        <v>436739</v>
       </c>
       <c r="R20" t="n">
-        <v>7027793</v>
+        <v>7028034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3022,21 +3079,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3045,51 +3092,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124133629</v>
+        <v>124138431</v>
       </c>
       <c r="B21" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3102,42 +3124,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436623</v>
+        <v>436653</v>
       </c>
       <c r="R21" t="n">
-        <v>7027760</v>
+        <v>7028028</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3164,26 +3181,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3192,51 +3194,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138449</v>
+        <v>124134174</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
+        <v>79898</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3245,41 +3222,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436602</v>
+        <v>436557</v>
       </c>
       <c r="R22" t="n">
-        <v>7027958</v>
+        <v>7027773</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3306,14 +3288,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3324,26 +3311,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124129618</v>
+        <v>124138449</v>
       </c>
       <c r="B23" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3356,42 +3368,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436474</v>
+        <v>436602</v>
       </c>
       <c r="R23" t="n">
-        <v>7027820</v>
+        <v>7027958</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3418,19 +3425,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3441,51 +3443,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138453</v>
+        <v>124138426</v>
       </c>
       <c r="B24" t="n">
-        <v>91683</v>
+        <v>90990</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3494,25 +3471,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3522,10 +3499,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436490</v>
+        <v>436760</v>
       </c>
       <c r="R24" t="n">
-        <v>7027974</v>
+        <v>7028081</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3584,10 +3561,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138481</v>
+        <v>124127075</v>
       </c>
       <c r="B25" t="n">
-        <v>88337</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3600,37 +3577,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436391</v>
+        <v>436458</v>
       </c>
       <c r="R25" t="n">
-        <v>7027787</v>
+        <v>7027708</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3657,11 +3639,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3670,26 +3662,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138466</v>
+        <v>124138428</v>
       </c>
       <c r="B26" t="n">
-        <v>91004</v>
+        <v>90990</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3702,21 +3719,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3726,10 +3743,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436589</v>
+        <v>436678</v>
       </c>
       <c r="R26" t="n">
-        <v>7027985</v>
+        <v>7028031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3788,10 +3805,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124132562</v>
+        <v>124130043</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3800,41 +3817,60 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436679</v>
+        <v>436564</v>
       </c>
       <c r="R27" t="n">
-        <v>7027841</v>
+        <v>7027844</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3863,7 +3899,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3873,12 +3909,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3893,26 +3924,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3930,10 +3941,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124134174</v>
+        <v>124133534</v>
       </c>
       <c r="B28" t="n">
-        <v>79898</v>
+        <v>79870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3942,46 +3953,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436557</v>
+        <v>436627</v>
       </c>
       <c r="R28" t="n">
-        <v>7027773</v>
+        <v>7027780</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4010,7 +4016,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4020,7 +4026,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4049,12 +4060,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4209,10 +4220,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124131669</v>
+        <v>124138434</v>
       </c>
       <c r="B30" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4225,42 +4236,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436701</v>
+        <v>436588</v>
       </c>
       <c r="R30" t="n">
-        <v>7027783</v>
+        <v>7027994</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4287,21 +4293,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4310,51 +4306,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124126749</v>
+        <v>124138466</v>
       </c>
       <c r="B31" t="n">
-        <v>57644</v>
+        <v>91004</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4367,51 +4338,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436643</v>
+        <v>436589</v>
       </c>
       <c r="R31" t="n">
-        <v>7027739</v>
+        <v>7027985</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4438,26 +4395,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4466,31 +4408,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138476</v>
+        <v>124131109</v>
       </c>
       <c r="B32" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4503,37 +4440,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436556</v>
+        <v>436775</v>
       </c>
       <c r="R32" t="n">
-        <v>7027990</v>
+        <v>7027895</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4560,11 +4497,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4573,26 +4520,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124131819</v>
+        <v>124138476</v>
       </c>
       <c r="B33" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4605,42 +4577,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436725</v>
+        <v>436556</v>
       </c>
       <c r="R33" t="n">
-        <v>7027833</v>
+        <v>7027990</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4667,21 +4634,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4690,51 +4647,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138426</v>
+        <v>124130402</v>
       </c>
       <c r="B34" t="n">
-        <v>90990</v>
+        <v>79905</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4743,41 +4675,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436760</v>
+        <v>436671</v>
       </c>
       <c r="R34" t="n">
-        <v>7028081</v>
+        <v>7027849</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4804,11 +4741,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4817,26 +4764,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124134617</v>
+        <v>124130731</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4849,34 +4821,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436450</v>
+        <v>436707</v>
       </c>
       <c r="R35" t="n">
-        <v>7027766</v>
+        <v>7027946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4908,7 +4894,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4918,12 +4904,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4938,26 +4919,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4975,10 +4936,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124131109</v>
+        <v>124131819</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4991,34 +4952,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436775</v>
+        <v>436725</v>
       </c>
       <c r="R36" t="n">
-        <v>7027895</v>
+        <v>7027833</v>
       </c>
       <c r="S36" t="n">
         <v>7</v>
@@ -5050,7 +5016,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5060,7 +5026,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5079,22 +5045,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5112,10 +5078,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124133243</v>
+        <v>124138453</v>
       </c>
       <c r="B37" t="n">
-        <v>79898</v>
+        <v>91683</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5124,46 +5090,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>67</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436634</v>
+        <v>436490</v>
       </c>
       <c r="R37" t="n">
-        <v>7027830</v>
+        <v>7027974</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5190,21 +5151,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5213,51 +5164,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138434</v>
+        <v>124134147</v>
       </c>
       <c r="B38" t="n">
-        <v>90990</v>
+        <v>79870</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5270,34 +5196,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436588</v>
+        <v>436555</v>
       </c>
       <c r="R38" t="n">
-        <v>7027994</v>
+        <v>7027775</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5327,11 +5258,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5340,26 +5281,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124134147</v>
+        <v>124138432</v>
       </c>
       <c r="B39" t="n">
-        <v>79870</v>
+        <v>90990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5372,39 +5338,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436555</v>
+        <v>436583</v>
       </c>
       <c r="R39" t="n">
-        <v>7027775</v>
+        <v>7028008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5434,21 +5395,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5457,51 +5408,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124138459</v>
+        <v>124130607</v>
       </c>
       <c r="B40" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5514,37 +5440,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436448</v>
+        <v>436700</v>
       </c>
       <c r="R40" t="n">
-        <v>7027953</v>
+        <v>7027918</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5571,14 +5497,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5589,26 +5520,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124134307</v>
+        <v>124131669</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5621,37 +5577,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436504</v>
+        <v>436701</v>
       </c>
       <c r="R41" t="n">
-        <v>7027727</v>
+        <v>7027783</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5680,7 +5641,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5690,7 +5651,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5709,22 +5670,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5742,10 +5703,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138436</v>
+        <v>124126749</v>
       </c>
       <c r="B42" t="n">
-        <v>90990</v>
+        <v>57644</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5758,37 +5719,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436408</v>
+        <v>436643</v>
       </c>
       <c r="R42" t="n">
-        <v>7027885</v>
+        <v>7027739</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5815,11 +5790,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5828,26 +5818,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124130731</v>
+        <v>124138474</v>
       </c>
       <c r="B43" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5860,48 +5855,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436707</v>
+        <v>436493</v>
       </c>
       <c r="R43" t="n">
-        <v>7027946</v>
+        <v>7027911</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5931,21 +5912,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5954,31 +5925,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124130402</v>
+        <v>124129618</v>
       </c>
       <c r="B44" t="n">
-        <v>79905</v>
+        <v>79869</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5987,31 +5953,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6020,13 +5986,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436671</v>
+        <v>436474</v>
       </c>
       <c r="R44" t="n">
-        <v>7027849</v>
+        <v>7027820</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6055,7 +6021,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6065,7 +6031,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6117,10 +6083,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124127075</v>
+        <v>124138452</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>90940</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6133,42 +6099,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436458</v>
+        <v>436732</v>
       </c>
       <c r="R45" t="n">
-        <v>7027708</v>
+        <v>7028026</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6195,21 +6156,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6218,51 +6169,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138428</v>
+        <v>124134617</v>
       </c>
       <c r="B46" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6275,34 +6201,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436678</v>
+        <v>436450</v>
       </c>
       <c r="R46" t="n">
-        <v>7028031</v>
+        <v>7027766</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6332,11 +6258,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6345,26 +6286,51 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138462</v>
+        <v>124130487</v>
       </c>
       <c r="B47" t="n">
-        <v>91435</v>
+        <v>57861</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6373,41 +6339,60 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436591</v>
+        <v>436684</v>
       </c>
       <c r="R47" t="n">
-        <v>7028013</v>
+        <v>7027902</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6434,11 +6419,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6447,26 +6442,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124133343</v>
+        <v>124126865</v>
       </c>
       <c r="B48" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6479,27 +6479,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6508,13 +6508,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436623</v>
+        <v>436624</v>
       </c>
       <c r="R48" t="n">
-        <v>7027816</v>
+        <v>7027776</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6553,12 +6553,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6577,22 +6572,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6610,10 +6605,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124133039</v>
+        <v>124132300</v>
       </c>
       <c r="B49" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6622,31 +6617,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6655,13 +6659,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436650</v>
+        <v>436689</v>
       </c>
       <c r="R49" t="n">
-        <v>7027809</v>
+        <v>7027839</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6690,7 +6694,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6700,7 +6704,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6715,26 +6724,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6752,10 +6741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124126865</v>
+        <v>124133039</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6768,27 +6757,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6797,13 +6786,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436624</v>
+        <v>436650</v>
       </c>
       <c r="R50" t="n">
-        <v>7027776</v>
+        <v>7027809</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6832,7 +6821,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6842,7 +6831,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6871,12 +6860,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6894,10 +6883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124132300</v>
+        <v>124133343</v>
       </c>
       <c r="B51" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6906,40 +6895,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6948,13 +6928,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436689</v>
+        <v>436623</v>
       </c>
       <c r="R51" t="n">
-        <v>7027839</v>
+        <v>7027816</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6983,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6993,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7013,6 +6993,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138459</v>
+        <v>124126979</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436448</v>
+        <v>436580</v>
       </c>
       <c r="R2" t="n">
-        <v>7027953</v>
+        <v>7027758</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +753,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,26 +781,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124126979</v>
+        <v>124138466</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91026</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +838,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436580</v>
+        <v>436589</v>
       </c>
       <c r="R3" t="n">
-        <v>7027758</v>
+        <v>7027985</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,26 +895,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,51 +908,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124134565</v>
+        <v>124131109</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,42 +940,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436416</v>
+        <v>436775</v>
       </c>
       <c r="R4" t="n">
-        <v>7027743</v>
+        <v>7027895</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1223,10 +1208,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124129992</v>
+        <v>124126749</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,37 +1224,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436580</v>
+        <v>436643</v>
       </c>
       <c r="R6" t="n">
-        <v>7027853</v>
+        <v>7027739</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1298,7 +1297,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1308,7 +1307,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1323,26 +1327,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1360,10 +1344,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138466</v>
+        <v>124138474</v>
       </c>
       <c r="B7" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1376,21 +1360,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1400,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436589</v>
+        <v>436493</v>
       </c>
       <c r="R7" t="n">
-        <v>7027985</v>
+        <v>7027911</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1462,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124134617</v>
+        <v>124134307</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1498,17 +1482,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436450</v>
+        <v>436504</v>
       </c>
       <c r="R8" t="n">
-        <v>7027766</v>
+        <v>7027727</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1537,7 +1521,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1547,12 +1531,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,10 +1583,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124134307</v>
+        <v>124130731</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1620,37 +1599,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436504</v>
+        <v>436707</v>
       </c>
       <c r="R9" t="n">
-        <v>7027727</v>
+        <v>7027946</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1672,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1682,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,26 +1697,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1741,7 +1714,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124129722</v>
+        <v>124132562</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1781,13 +1754,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436509</v>
+        <v>436679</v>
       </c>
       <c r="R10" t="n">
-        <v>7027814</v>
+        <v>7027841</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1816,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1826,7 +1799,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1878,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138449</v>
+        <v>124130607</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1894,37 +1872,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436602</v>
+        <v>436700</v>
       </c>
       <c r="R11" t="n">
-        <v>7027958</v>
+        <v>7027918</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1951,14 +1929,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,26 +1952,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138425</v>
+        <v>124133534</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2001,37 +2009,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436739</v>
+        <v>436627</v>
       </c>
       <c r="R12" t="n">
-        <v>7028034</v>
+        <v>7027780</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2058,11 +2066,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2071,26 +2094,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124138481</v>
+        <v>124134617</v>
       </c>
       <c r="B13" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2103,34 +2151,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436391</v>
+        <v>436450</v>
       </c>
       <c r="R13" t="n">
-        <v>7027787</v>
+        <v>7027766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2160,11 +2208,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2173,26 +2236,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124131669</v>
+        <v>124130043</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2201,31 +2289,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2234,13 +2336,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436701</v>
+        <v>436564</v>
       </c>
       <c r="R14" t="n">
-        <v>7027783</v>
+        <v>7027844</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2269,7 +2371,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2279,7 +2381,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2294,26 +2396,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2331,10 +2413,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138478</v>
+        <v>124138459</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2347,21 +2429,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2371,10 +2453,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436440</v>
+        <v>436448</v>
       </c>
       <c r="R15" t="n">
-        <v>7027952</v>
+        <v>7027953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,6 +2489,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,10 +2520,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138452</v>
+        <v>124138425</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2449,21 +2536,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2473,10 +2560,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436732</v>
+        <v>436739</v>
       </c>
       <c r="R16" t="n">
-        <v>7028026</v>
+        <v>7028034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2535,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138432</v>
+        <v>124138434</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2575,10 +2662,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436583</v>
+        <v>436588</v>
       </c>
       <c r="R17" t="n">
-        <v>7028008</v>
+        <v>7027994</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2637,10 +2724,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124133243</v>
+        <v>124133629</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2649,31 +2736,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2682,10 +2769,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436634</v>
+        <v>436623</v>
       </c>
       <c r="R18" t="n">
-        <v>7027830</v>
+        <v>7027760</v>
       </c>
       <c r="S18" t="n">
         <v>11</v>
@@ -2717,7 +2804,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2727,7 +2814,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2756,12 +2848,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2779,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124131523</v>
+        <v>124130109</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2795,37 +2887,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436749</v>
+        <v>436613</v>
       </c>
       <c r="R19" t="n">
-        <v>7027816</v>
+        <v>7027858</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2854,7 +2956,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2864,7 +2966,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2893,12 +3000,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2916,10 +3023,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138476</v>
+        <v>124138453</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>91705</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2928,25 +3035,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2956,10 +3063,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436556</v>
+        <v>436490</v>
       </c>
       <c r="R20" t="n">
-        <v>7027990</v>
+        <v>7027974</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3018,10 +3125,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124130109</v>
+        <v>124134565</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3034,16 +3141,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3057,24 +3164,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436613</v>
+        <v>436416</v>
       </c>
       <c r="R21" t="n">
-        <v>7027858</v>
+        <v>7027743</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3103,7 +3205,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3113,12 +3215,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3147,12 +3249,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3170,10 +3272,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124127075</v>
+        <v>124133243</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3182,25 +3284,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3211,17 +3313,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436458</v>
+        <v>436634</v>
       </c>
       <c r="R22" t="n">
-        <v>7027708</v>
+        <v>7027830</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3250,7 +3352,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3260,7 +3362,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,22 +3381,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3312,10 +3414,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124130043</v>
+        <v>124129449</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3324,60 +3426,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436564</v>
+        <v>436417</v>
       </c>
       <c r="R23" t="n">
-        <v>7027844</v>
+        <v>7027793</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3406,7 +3489,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3416,7 +3499,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3431,6 +3514,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3448,10 +3551,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124130731</v>
+        <v>124138478</v>
       </c>
       <c r="B24" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3464,48 +3567,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436707</v>
+        <v>436440</v>
       </c>
       <c r="R24" t="n">
-        <v>7027946</v>
+        <v>7027952</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3535,21 +3624,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3558,31 +3637,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138436</v>
+        <v>124129722</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3595,37 +3669,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436408</v>
+        <v>436509</v>
       </c>
       <c r="R25" t="n">
-        <v>7027885</v>
+        <v>7027814</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3652,11 +3726,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3665,16 +3749,41 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3823,10 +3932,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124126749</v>
+        <v>124130487</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3835,35 +3944,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3877,10 +3991,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436643</v>
+        <v>436684</v>
       </c>
       <c r="R27" t="n">
-        <v>7027739</v>
+        <v>7027902</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3912,7 +4026,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3922,12 +4036,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3959,10 +4068,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138474</v>
+        <v>124138423</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3975,21 +4084,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3999,10 +4108,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436493</v>
+        <v>436415</v>
       </c>
       <c r="R28" t="n">
-        <v>7027911</v>
+        <v>7027827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4061,10 +4170,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138434</v>
+        <v>124131523</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4077,37 +4186,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436588</v>
+        <v>436749</v>
       </c>
       <c r="R29" t="n">
-        <v>7027994</v>
+        <v>7027816</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4134,11 +4243,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4147,26 +4266,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124131819</v>
+        <v>124138462</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>91457</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4175,46 +4319,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436725</v>
+        <v>436591</v>
       </c>
       <c r="R30" t="n">
-        <v>7027833</v>
+        <v>7028013</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4241,21 +4380,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4264,51 +4393,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124133534</v>
+        <v>124129618</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4321,37 +4425,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436627</v>
+        <v>436474</v>
       </c>
       <c r="R31" t="n">
-        <v>7027780</v>
+        <v>7027820</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4380,7 +4489,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4390,12 +4499,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4424,12 +4528,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4447,10 +4551,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124132562</v>
+        <v>124138431</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4463,37 +4567,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436679</v>
+        <v>436653</v>
       </c>
       <c r="R32" t="n">
-        <v>7027841</v>
+        <v>7028028</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4520,26 +4624,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4548,48 +4637,23 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138428</v>
+        <v>124138436</v>
       </c>
       <c r="B33" t="n">
         <v>91012</v>
@@ -4629,10 +4693,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436678</v>
+        <v>436408</v>
       </c>
       <c r="R33" t="n">
-        <v>7028031</v>
+        <v>7027885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4691,10 +4755,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138423</v>
+        <v>124129992</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4707,37 +4771,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436415</v>
+        <v>436580</v>
       </c>
       <c r="R34" t="n">
-        <v>7027827</v>
+        <v>7027853</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4764,11 +4828,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4777,26 +4851,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124130487</v>
+        <v>124131669</v>
       </c>
       <c r="B35" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4805,45 +4904,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4852,13 +4937,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436684</v>
+        <v>436701</v>
       </c>
       <c r="R35" t="n">
-        <v>7027902</v>
+        <v>7027783</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4887,7 +4972,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4897,7 +4982,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4912,6 +4997,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4929,10 +5034,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138431</v>
+        <v>124138452</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4945,21 +5050,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4969,10 +5074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436653</v>
+        <v>436732</v>
       </c>
       <c r="R36" t="n">
-        <v>7028028</v>
+        <v>7028026</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5031,7 +5136,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124129618</v>
+        <v>124131819</v>
       </c>
       <c r="B37" t="n">
         <v>79891</v>
@@ -5076,13 +5181,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436474</v>
+        <v>436725</v>
       </c>
       <c r="R37" t="n">
-        <v>7027820</v>
+        <v>7027833</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5111,7 +5216,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5121,7 +5226,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5173,10 +5278,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124133629</v>
+        <v>124138426</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5189,42 +5294,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436623</v>
+        <v>436760</v>
       </c>
       <c r="R38" t="n">
-        <v>7027760</v>
+        <v>7028081</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5251,26 +5351,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5279,51 +5364,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138453</v>
+        <v>124130826</v>
       </c>
       <c r="B39" t="n">
-        <v>91705</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5332,41 +5392,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>67</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436490</v>
+        <v>436743</v>
       </c>
       <c r="R39" t="n">
-        <v>7027974</v>
+        <v>7027889</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5393,11 +5458,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5406,26 +5481,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124138462</v>
+        <v>124134174</v>
       </c>
       <c r="B40" t="n">
-        <v>91457</v>
+        <v>79920</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5434,41 +5534,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436591</v>
+        <v>436557</v>
       </c>
       <c r="R40" t="n">
-        <v>7028013</v>
+        <v>7027773</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5495,11 +5600,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5508,26 +5623,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124130607</v>
+        <v>124138476</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5540,37 +5680,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436700</v>
+        <v>436556</v>
       </c>
       <c r="R41" t="n">
-        <v>7027918</v>
+        <v>7027990</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5597,21 +5737,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5620,51 +5750,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124129449</v>
+        <v>124138481</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5677,34 +5782,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436417</v>
+        <v>436391</v>
       </c>
       <c r="R42" t="n">
-        <v>7027793</v>
+        <v>7027787</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5734,21 +5839,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5757,51 +5852,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124134174</v>
+        <v>124138432</v>
       </c>
       <c r="B43" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5810,46 +5880,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436557</v>
+        <v>436583</v>
       </c>
       <c r="R43" t="n">
-        <v>7027773</v>
+        <v>7028008</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5876,21 +5941,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5899,41 +5954,16 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6082,7 +6112,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138426</v>
+        <v>124138428</v>
       </c>
       <c r="B45" t="n">
         <v>91012</v>
@@ -6122,10 +6152,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436760</v>
+        <v>436678</v>
       </c>
       <c r="R45" t="n">
-        <v>7028081</v>
+        <v>7028031</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6184,7 +6214,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124131109</v>
+        <v>124127075</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -6218,16 +6248,21 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436775</v>
+        <v>436458</v>
       </c>
       <c r="R46" t="n">
-        <v>7027895</v>
+        <v>7027708</v>
       </c>
       <c r="S46" t="n">
         <v>7</v>
@@ -6259,7 +6294,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6269,7 +6304,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6321,10 +6356,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124130826</v>
+        <v>124138449</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6337,42 +6372,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436743</v>
+        <v>436602</v>
       </c>
       <c r="R47" t="n">
-        <v>7027889</v>
+        <v>7027958</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6399,19 +6429,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:20</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6422,51 +6447,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124133343</v>
+        <v>124126865</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6479,27 +6479,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6508,13 +6508,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436623</v>
+        <v>436624</v>
       </c>
       <c r="R48" t="n">
-        <v>7027816</v>
+        <v>7027776</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6553,12 +6553,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6577,22 +6572,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6610,10 +6605,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124126865</v>
+        <v>124133343</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6626,27 +6621,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6655,13 +6650,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436624</v>
+        <v>436623</v>
       </c>
       <c r="R49" t="n">
-        <v>7027776</v>
+        <v>7027816</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6690,7 +6685,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6700,7 +6695,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6719,22 +6719,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -822,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138466</v>
+        <v>124132562</v>
       </c>
       <c r="B3" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436589</v>
+        <v>436679</v>
       </c>
       <c r="R3" t="n">
-        <v>7027985</v>
+        <v>7027841</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,11 +895,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,26 +923,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124131109</v>
+        <v>124130109</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,34 +980,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436775</v>
+        <v>436613</v>
       </c>
       <c r="R4" t="n">
-        <v>7027895</v>
+        <v>7027858</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -999,7 +1049,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1059,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,12 +1093,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,10 +1116,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124133665</v>
+        <v>124133629</v>
       </c>
       <c r="B5" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,25 +1128,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,13 +1161,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436624</v>
+        <v>436623</v>
       </c>
       <c r="R5" t="n">
-        <v>7027776</v>
+        <v>7027760</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,7 +1196,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1151,7 +1206,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1185,12 +1240,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1208,10 +1263,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124126749</v>
+        <v>124131669</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,36 +1279,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1262,13 +1308,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436643</v>
+        <v>436701</v>
       </c>
       <c r="R6" t="n">
-        <v>7027739</v>
+        <v>7027783</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1297,7 +1343,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,12 +1353,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,6 +1368,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1344,10 +1405,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138474</v>
+        <v>124138452</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1360,21 +1421,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1384,10 +1445,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436493</v>
+        <v>436732</v>
       </c>
       <c r="R7" t="n">
-        <v>7027911</v>
+        <v>7028026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1446,10 +1507,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124134307</v>
+        <v>124130487</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,41 +1519,60 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436504</v>
+        <v>436684</v>
       </c>
       <c r="R8" t="n">
-        <v>7027727</v>
+        <v>7027902</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1521,7 +1601,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1531,7 +1611,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,26 +1626,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1583,10 +1643,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124130731</v>
+        <v>124129449</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,48 +1659,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436707</v>
+        <v>436417</v>
       </c>
       <c r="R9" t="n">
-        <v>7027946</v>
+        <v>7027793</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1718,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1682,7 +1728,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,6 +1743,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,10 +1780,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124132562</v>
+        <v>124131819</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1730,37 +1796,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436679</v>
+        <v>436725</v>
       </c>
       <c r="R10" t="n">
-        <v>7027841</v>
+        <v>7027833</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1789,7 +1860,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1799,12 +1870,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1823,22 +1889,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1856,7 +1922,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124130607</v>
+        <v>124129722</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1896,13 +1962,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436700</v>
+        <v>436509</v>
       </c>
       <c r="R11" t="n">
-        <v>7027918</v>
+        <v>7027814</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1931,7 +1997,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1941,7 +2007,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2135,10 +2201,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124134617</v>
+        <v>124130043</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2147,41 +2213,60 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436450</v>
+        <v>436564</v>
       </c>
       <c r="R13" t="n">
-        <v>7027766</v>
+        <v>7027844</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2210,7 +2295,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2220,12 +2305,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,26 +2320,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2277,10 +2337,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124130043</v>
+        <v>124138425</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2289,60 +2349,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436564</v>
+        <v>436739</v>
       </c>
       <c r="R14" t="n">
-        <v>7027844</v>
+        <v>7028034</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2369,21 +2410,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2392,31 +2423,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138459</v>
+        <v>124130731</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2429,16 +2455,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2446,17 +2472,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436448</v>
+        <v>436707</v>
       </c>
       <c r="R15" t="n">
-        <v>7027953</v>
+        <v>7027946</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2486,14 +2526,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2504,26 +2549,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138425</v>
+        <v>124131523</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2536,37 +2586,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436739</v>
+        <v>436749</v>
       </c>
       <c r="R16" t="n">
-        <v>7028034</v>
+        <v>7027816</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2593,11 +2643,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2606,26 +2666,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138434</v>
+        <v>124127075</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2638,37 +2723,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436588</v>
+        <v>436458</v>
       </c>
       <c r="R17" t="n">
-        <v>7027994</v>
+        <v>7027708</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2695,11 +2785,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2708,26 +2808,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124133629</v>
+        <v>124138466</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>91026</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2740,42 +2865,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436623</v>
+        <v>436589</v>
       </c>
       <c r="R18" t="n">
-        <v>7027760</v>
+        <v>7027985</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2802,26 +2922,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2830,51 +2935,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124130109</v>
+        <v>124138423</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2887,47 +2967,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436613</v>
+        <v>436415</v>
       </c>
       <c r="R19" t="n">
-        <v>7027858</v>
+        <v>7027827</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2954,26 +3024,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2982,51 +3037,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138453</v>
+        <v>124138462</v>
       </c>
       <c r="B20" t="n">
-        <v>91705</v>
+        <v>91457</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3039,21 +3069,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3063,10 +3093,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436490</v>
+        <v>436591</v>
       </c>
       <c r="R20" t="n">
-        <v>7027974</v>
+        <v>7028013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3125,10 +3155,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124134565</v>
+        <v>124138459</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3141,16 +3171,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3159,21 +3189,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436416</v>
+        <v>436448</v>
       </c>
       <c r="R21" t="n">
-        <v>7027743</v>
+        <v>7027953</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3203,24 +3228,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,51 +3246,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124133243</v>
+        <v>124138476</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3284,46 +3274,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436634</v>
+        <v>436556</v>
       </c>
       <c r="R22" t="n">
-        <v>7027830</v>
+        <v>7027990</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3350,21 +3335,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3373,51 +3348,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124129449</v>
+        <v>124133665</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3426,20 +3376,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3448,19 +3398,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436417</v>
+        <v>436624</v>
       </c>
       <c r="R23" t="n">
-        <v>7027793</v>
+        <v>7027776</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3489,7 +3444,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3499,7 +3454,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3518,22 +3478,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3551,10 +3511,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138478</v>
+        <v>124138449</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3567,21 +3527,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3591,10 +3551,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436440</v>
+        <v>436602</v>
       </c>
       <c r="R24" t="n">
-        <v>7027952</v>
+        <v>7027958</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3627,6 +3587,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3653,10 +3618,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124129722</v>
+        <v>124129618</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3669,37 +3634,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436509</v>
+        <v>436474</v>
       </c>
       <c r="R25" t="n">
-        <v>7027814</v>
+        <v>7027820</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3728,7 +3698,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3738,7 +3708,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3757,22 +3727,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3790,10 +3760,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124130402</v>
+        <v>124138428</v>
       </c>
       <c r="B26" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3802,46 +3772,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436671</v>
+        <v>436678</v>
       </c>
       <c r="R26" t="n">
-        <v>7027849</v>
+        <v>7028031</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3868,21 +3833,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3891,51 +3846,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124130487</v>
+        <v>124138434</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3944,60 +3874,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436684</v>
+        <v>436588</v>
       </c>
       <c r="R27" t="n">
-        <v>7027902</v>
+        <v>7027994</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4024,21 +3935,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4047,28 +3948,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138423</v>
+        <v>124138426</v>
       </c>
       <c r="B28" t="n">
         <v>91012</v>
@@ -4108,10 +4004,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436415</v>
+        <v>436760</v>
       </c>
       <c r="R28" t="n">
-        <v>7027827</v>
+        <v>7028081</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4170,10 +4066,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124131523</v>
+        <v>124138436</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4186,37 +4082,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436749</v>
+        <v>436408</v>
       </c>
       <c r="R29" t="n">
-        <v>7027816</v>
+        <v>7027885</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4243,21 +4139,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4266,51 +4152,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138462</v>
+        <v>124131109</v>
       </c>
       <c r="B30" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4319,41 +4180,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436591</v>
+        <v>436775</v>
       </c>
       <c r="R30" t="n">
-        <v>7028013</v>
+        <v>7027895</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4380,11 +4241,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4393,26 +4264,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124129618</v>
+        <v>124126749</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4425,27 +4321,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4454,13 +4359,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436474</v>
+        <v>436643</v>
       </c>
       <c r="R31" t="n">
-        <v>7027820</v>
+        <v>7027739</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4489,7 +4394,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4499,7 +4404,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4514,26 +4424,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4551,10 +4441,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138431</v>
+        <v>124138474</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4567,21 +4457,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4591,10 +4481,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436653</v>
+        <v>436493</v>
       </c>
       <c r="R32" t="n">
-        <v>7028028</v>
+        <v>7027911</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4653,10 +4543,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138436</v>
+        <v>124130607</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4669,37 +4559,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436408</v>
+        <v>436700</v>
       </c>
       <c r="R33" t="n">
-        <v>7027885</v>
+        <v>7027918</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4726,11 +4616,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4739,26 +4639,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124129992</v>
+        <v>124138481</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4771,37 +4696,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436580</v>
+        <v>436391</v>
       </c>
       <c r="R34" t="n">
-        <v>7027853</v>
+        <v>7027787</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4828,21 +4753,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4851,51 +4766,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124131669</v>
+        <v>124138478</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4908,42 +4798,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436701</v>
+        <v>436440</v>
       </c>
       <c r="R35" t="n">
-        <v>7027783</v>
+        <v>7027952</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4970,21 +4855,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4993,51 +4868,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138452</v>
+        <v>124130826</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5050,37 +4900,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436732</v>
+        <v>436743</v>
       </c>
       <c r="R36" t="n">
-        <v>7028026</v>
+        <v>7027889</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5107,11 +4962,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5120,26 +4985,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124131819</v>
+        <v>124138431</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5152,42 +5042,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436725</v>
+        <v>436653</v>
       </c>
       <c r="R37" t="n">
-        <v>7027833</v>
+        <v>7028028</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5214,21 +5099,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5237,51 +5112,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138426</v>
+        <v>124133243</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5290,41 +5140,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436760</v>
+        <v>436634</v>
       </c>
       <c r="R38" t="n">
-        <v>7028081</v>
+        <v>7027830</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5351,11 +5206,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5364,26 +5229,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124130826</v>
+        <v>124130402</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>79927</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5392,31 +5282,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5425,13 +5315,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436743</v>
+        <v>436671</v>
       </c>
       <c r="R39" t="n">
-        <v>7027889</v>
+        <v>7027849</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5460,7 +5350,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5470,7 +5360,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5489,22 +5379,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5522,10 +5412,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124134174</v>
+        <v>124134147</v>
       </c>
       <c r="B40" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5534,31 +5424,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5567,13 +5457,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436557</v>
+        <v>436555</v>
       </c>
       <c r="R40" t="n">
-        <v>7027773</v>
+        <v>7027775</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5602,7 +5492,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5612,7 +5502,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5664,10 +5554,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138476</v>
+        <v>124134565</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5680,34 +5570,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436556</v>
+        <v>436416</v>
       </c>
       <c r="R41" t="n">
-        <v>7027990</v>
+        <v>7027743</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5737,11 +5632,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5660,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138481</v>
+        <v>124134174</v>
       </c>
       <c r="B42" t="n">
-        <v>88359</v>
+        <v>79920</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5778,41 +5713,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436391</v>
+        <v>436557</v>
       </c>
       <c r="R42" t="n">
-        <v>7027787</v>
+        <v>7027773</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5839,11 +5779,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5852,16 +5802,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5970,10 +5945,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124134147</v>
+        <v>124134617</v>
       </c>
       <c r="B44" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5986,39 +5961,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436555</v>
+        <v>436450</v>
       </c>
       <c r="R44" t="n">
-        <v>7027775</v>
+        <v>7027766</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6050,7 +6020,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6060,7 +6030,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6079,22 +6054,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6112,10 +6087,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138428</v>
+        <v>124134307</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6128,37 +6103,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436678</v>
+        <v>436504</v>
       </c>
       <c r="R45" t="n">
-        <v>7028031</v>
+        <v>7027727</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6185,11 +6160,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6198,23 +6183,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124127075</v>
+        <v>124129992</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -6248,24 +6258,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436458</v>
+        <v>436580</v>
       </c>
       <c r="R46" t="n">
-        <v>7027708</v>
+        <v>7027853</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6294,7 +6299,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6304,7 +6309,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6333,12 +6338,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6356,10 +6361,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138449</v>
+        <v>124138453</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6368,25 +6373,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6396,10 +6401,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436602</v>
+        <v>436490</v>
       </c>
       <c r="R47" t="n">
-        <v>7027958</v>
+        <v>7027974</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6432,11 +6437,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6463,10 +6463,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124126865</v>
+        <v>124133343</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6479,27 +6479,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6508,13 +6508,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436624</v>
+        <v>436623</v>
       </c>
       <c r="R48" t="n">
-        <v>7027776</v>
+        <v>7027816</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6553,7 +6553,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6572,22 +6577,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6605,10 +6610,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124133343</v>
+        <v>124126865</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6621,27 +6626,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6650,13 +6655,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436623</v>
+        <v>436624</v>
       </c>
       <c r="R49" t="n">
-        <v>7027816</v>
+        <v>7027776</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6685,7 +6690,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6695,12 +6700,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6719,22 +6719,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124126979</v>
+        <v>124138459</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436580</v>
+        <v>436448</v>
       </c>
       <c r="R2" t="n">
-        <v>7027758</v>
+        <v>7027953</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,24 +748,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,51 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124132562</v>
+        <v>124131669</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436679</v>
+        <v>436701</v>
       </c>
       <c r="R3" t="n">
-        <v>7027841</v>
+        <v>7027783</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -897,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,22 +891,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124130109</v>
+        <v>124130043</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -976,20 +936,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -997,10 +957,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1014,13 +983,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436613</v>
+        <v>436564</v>
       </c>
       <c r="R4" t="n">
-        <v>7027858</v>
+        <v>7027844</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,12 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,26 +1043,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1116,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124133629</v>
+        <v>124138425</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1132,42 +1076,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436623</v>
+        <v>436739</v>
       </c>
       <c r="R5" t="n">
-        <v>7027760</v>
+        <v>7028034</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1194,26 +1133,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1222,51 +1146,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124131669</v>
+        <v>124130402</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1275,31 +1174,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436701</v>
+        <v>436671</v>
       </c>
       <c r="R6" t="n">
-        <v>7027783</v>
+        <v>7027849</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1343,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1353,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1405,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138452</v>
+        <v>124138434</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1421,21 +1320,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1445,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436732</v>
+        <v>436588</v>
       </c>
       <c r="R7" t="n">
-        <v>7028026</v>
+        <v>7027994</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1507,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124130487</v>
+        <v>124134147</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1519,45 +1418,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1566,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436684</v>
+        <v>436555</v>
       </c>
       <c r="R8" t="n">
-        <v>7027902</v>
+        <v>7027775</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1601,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1611,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,6 +1511,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1643,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124129449</v>
+        <v>124138449</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1659,34 +1564,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436417</v>
+        <v>436602</v>
       </c>
       <c r="R9" t="n">
-        <v>7027793</v>
+        <v>7027958</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1716,19 +1621,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,51 +1639,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124131819</v>
+        <v>124138452</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1796,42 +1671,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436725</v>
+        <v>436732</v>
       </c>
       <c r="R10" t="n">
-        <v>7027833</v>
+        <v>7028026</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1858,21 +1728,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1881,48 +1741,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124129722</v>
+        <v>124127075</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1956,19 +1791,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436509</v>
+        <v>436458</v>
       </c>
       <c r="R11" t="n">
-        <v>7027814</v>
+        <v>7027708</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1997,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2007,7 +1847,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2036,12 +1876,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2059,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124133534</v>
+        <v>124138436</v>
       </c>
       <c r="B12" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2075,37 +1915,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436627</v>
+        <v>436408</v>
       </c>
       <c r="R12" t="n">
-        <v>7027780</v>
+        <v>7027885</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2132,26 +1972,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2160,51 +1985,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124130043</v>
+        <v>124131819</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,45 +2013,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2260,13 +2046,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436564</v>
+        <v>436725</v>
       </c>
       <c r="R13" t="n">
-        <v>7027844</v>
+        <v>7027833</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2295,7 +2081,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2305,7 +2091,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2320,6 +2106,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2337,10 +2143,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138425</v>
+        <v>124126749</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2353,37 +2159,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436739</v>
+        <v>436643</v>
       </c>
       <c r="R14" t="n">
-        <v>7028034</v>
+        <v>7027739</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2410,11 +2230,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2423,26 +2258,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124130731</v>
+        <v>124130109</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2455,16 +2295,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2472,14 +2312,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2493,13 +2329,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436707</v>
+        <v>436613</v>
       </c>
       <c r="R15" t="n">
-        <v>7027946</v>
+        <v>7027858</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2528,7 +2364,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2538,7 +2374,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2553,6 +2394,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2570,10 +2431,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124131523</v>
+        <v>124138474</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2586,37 +2447,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436749</v>
+        <v>436493</v>
       </c>
       <c r="R16" t="n">
-        <v>7027816</v>
+        <v>7027911</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2643,21 +2504,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2666,51 +2517,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124127075</v>
+        <v>124138426</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2723,42 +2549,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436458</v>
+        <v>436760</v>
       </c>
       <c r="R17" t="n">
-        <v>7027708</v>
+        <v>7028081</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2785,21 +2606,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2808,51 +2619,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138466</v>
+        <v>124138481</v>
       </c>
       <c r="B18" t="n">
-        <v>91026</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2865,21 +2651,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2889,10 +2675,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436589</v>
+        <v>436391</v>
       </c>
       <c r="R18" t="n">
-        <v>7027985</v>
+        <v>7027787</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2951,7 +2737,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138423</v>
+        <v>124138432</v>
       </c>
       <c r="B19" t="n">
         <v>91012</v>
@@ -2991,10 +2777,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436415</v>
+        <v>436583</v>
       </c>
       <c r="R19" t="n">
-        <v>7027827</v>
+        <v>7028008</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3053,10 +2839,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138462</v>
+        <v>124131109</v>
       </c>
       <c r="B20" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3065,41 +2851,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436591</v>
+        <v>436775</v>
       </c>
       <c r="R20" t="n">
-        <v>7028013</v>
+        <v>7027895</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3126,11 +2912,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3139,26 +2935,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138459</v>
+        <v>124134174</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3167,41 +2988,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436448</v>
+        <v>436557</v>
       </c>
       <c r="R21" t="n">
-        <v>7027953</v>
+        <v>7027773</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3228,14 +3054,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3246,26 +3077,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138476</v>
+        <v>124138431</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3278,21 +3134,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3302,10 +3158,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436556</v>
+        <v>436653</v>
       </c>
       <c r="R22" t="n">
-        <v>7027990</v>
+        <v>7028028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3364,10 +3220,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124133665</v>
+        <v>124133629</v>
       </c>
       <c r="B23" t="n">
-        <v>79926</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3376,25 +3232,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3409,13 +3265,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436624</v>
+        <v>436623</v>
       </c>
       <c r="R23" t="n">
-        <v>7027776</v>
+        <v>7027760</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3444,7 +3300,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3454,7 +3310,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3488,12 +3344,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3511,10 +3367,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138449</v>
+        <v>124134617</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3527,34 +3383,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436602</v>
+        <v>436450</v>
       </c>
       <c r="R24" t="n">
-        <v>7027958</v>
+        <v>7027766</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3584,14 +3440,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3602,26 +3468,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124129618</v>
+        <v>124129992</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3634,42 +3525,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436474</v>
+        <v>436580</v>
       </c>
       <c r="R25" t="n">
-        <v>7027820</v>
+        <v>7027853</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3698,7 +3584,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3708,7 +3594,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3727,22 +3613,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3760,10 +3646,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138428</v>
+        <v>124138462</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3772,25 +3658,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3800,10 +3686,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436678</v>
+        <v>436591</v>
       </c>
       <c r="R26" t="n">
-        <v>7028031</v>
+        <v>7028013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3862,7 +3748,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138434</v>
+        <v>124138428</v>
       </c>
       <c r="B27" t="n">
         <v>91012</v>
@@ -3902,10 +3788,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436588</v>
+        <v>436678</v>
       </c>
       <c r="R27" t="n">
-        <v>7027994</v>
+        <v>7028031</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3964,10 +3850,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138426</v>
+        <v>124133243</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3976,41 +3862,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436760</v>
+        <v>436634</v>
       </c>
       <c r="R28" t="n">
-        <v>7028081</v>
+        <v>7027830</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4037,11 +3928,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4050,26 +3951,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138436</v>
+        <v>124138476</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4082,21 +4008,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4106,10 +4032,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436408</v>
+        <v>436556</v>
       </c>
       <c r="R29" t="n">
-        <v>7027885</v>
+        <v>7027990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4168,10 +4094,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124131109</v>
+        <v>124138453</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4180,41 +4106,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436775</v>
+        <v>436490</v>
       </c>
       <c r="R30" t="n">
-        <v>7027895</v>
+        <v>7027974</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4241,21 +4167,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4264,51 +4180,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124126749</v>
+        <v>124138423</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4321,51 +4212,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436643</v>
+        <v>436415</v>
       </c>
       <c r="R31" t="n">
-        <v>7027739</v>
+        <v>7027827</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4392,26 +4269,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4420,31 +4282,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138474</v>
+        <v>124132562</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4457,37 +4314,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436493</v>
+        <v>436679</v>
       </c>
       <c r="R32" t="n">
-        <v>7027911</v>
+        <v>7027841</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4514,11 +4371,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4527,16 +4399,41 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4680,10 +4577,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138481</v>
+        <v>124131523</v>
       </c>
       <c r="B34" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4696,37 +4593,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436391</v>
+        <v>436749</v>
       </c>
       <c r="R34" t="n">
-        <v>7027787</v>
+        <v>7027816</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4753,11 +4650,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4766,26 +4673,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138478</v>
+        <v>124133665</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>79926</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4794,41 +4726,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436440</v>
+        <v>436624</v>
       </c>
       <c r="R35" t="n">
-        <v>7027952</v>
+        <v>7027776</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4855,11 +4792,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4868,26 +4820,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124130826</v>
+        <v>124126979</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4900,27 +4877,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4929,13 +4906,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436743</v>
+        <v>436580</v>
       </c>
       <c r="R36" t="n">
-        <v>7027889</v>
+        <v>7027758</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4964,7 +4941,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4974,7 +4951,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5003,12 +4985,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5026,10 +5008,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138431</v>
+        <v>124130731</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5042,34 +5024,48 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436653</v>
+        <v>436707</v>
       </c>
       <c r="R37" t="n">
-        <v>7028028</v>
+        <v>7027946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5099,11 +5095,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5112,26 +5118,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124133243</v>
+        <v>124133534</v>
       </c>
       <c r="B38" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5140,43 +5151,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436634</v>
+        <v>436627</v>
       </c>
       <c r="R38" t="n">
-        <v>7027830</v>
+        <v>7027780</v>
       </c>
       <c r="S38" t="n">
         <v>11</v>
@@ -5208,7 +5214,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5218,7 +5224,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,10 +5281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124130402</v>
+        <v>124129722</v>
       </c>
       <c r="B39" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5282,46 +5293,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436671</v>
+        <v>436509</v>
       </c>
       <c r="R39" t="n">
-        <v>7027849</v>
+        <v>7027814</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5350,7 +5356,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5360,7 +5366,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5379,22 +5385,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5412,10 +5418,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124134147</v>
+        <v>124130826</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5428,27 +5434,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5457,13 +5463,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436555</v>
+        <v>436743</v>
       </c>
       <c r="R40" t="n">
-        <v>7027775</v>
+        <v>7027889</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5492,7 +5498,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5502,7 +5508,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5521,22 +5527,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5554,10 +5560,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124134565</v>
+        <v>124129449</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5570,39 +5576,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436416</v>
+        <v>436417</v>
       </c>
       <c r="R41" t="n">
-        <v>7027743</v>
+        <v>7027793</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5634,7 +5635,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5644,12 +5645,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5678,12 +5674,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5701,10 +5697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124134174</v>
+        <v>124130487</v>
       </c>
       <c r="B42" t="n">
-        <v>79920</v>
+        <v>57883</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5717,27 +5713,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5746,13 +5756,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436557</v>
+        <v>436684</v>
       </c>
       <c r="R42" t="n">
-        <v>7027773</v>
+        <v>7027902</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5781,7 +5791,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5791,7 +5801,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5806,26 +5816,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5843,10 +5833,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138432</v>
+        <v>124138466</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5859,21 +5849,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5883,10 +5873,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436583</v>
+        <v>436589</v>
       </c>
       <c r="R43" t="n">
-        <v>7028008</v>
+        <v>7027985</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5945,10 +5935,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124134617</v>
+        <v>124138478</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5961,34 +5951,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436450</v>
+        <v>436440</v>
       </c>
       <c r="R44" t="n">
-        <v>7027766</v>
+        <v>7027952</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6018,26 +6008,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6046,51 +6021,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124134307</v>
+        <v>124134565</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6103,37 +6053,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436504</v>
+        <v>436416</v>
       </c>
       <c r="R45" t="n">
-        <v>7027727</v>
+        <v>7027743</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6162,7 +6117,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6172,7 +6127,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6201,12 +6161,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6224,7 +6184,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124129992</v>
+        <v>124134307</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -6260,14 +6220,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436580</v>
+        <v>436504</v>
       </c>
       <c r="R46" t="n">
-        <v>7027853</v>
+        <v>7027727</v>
       </c>
       <c r="S46" t="n">
         <v>11</v>
@@ -6299,7 +6259,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6309,7 +6269,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6361,10 +6321,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138453</v>
+        <v>124129618</v>
       </c>
       <c r="B47" t="n">
-        <v>91705</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6373,41 +6333,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436490</v>
+        <v>436474</v>
       </c>
       <c r="R47" t="n">
-        <v>7027974</v>
+        <v>7027820</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6434,11 +6399,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6447,26 +6422,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124133343</v>
+        <v>124132300</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6475,31 +6475,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6508,13 +6517,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436623</v>
+        <v>436689</v>
       </c>
       <c r="R48" t="n">
-        <v>7027816</v>
+        <v>7027839</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6543,7 +6552,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6553,12 +6562,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6573,26 +6582,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6894,10 +6883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124132300</v>
+        <v>124133343</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6906,40 +6895,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6948,13 +6928,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436689</v>
+        <v>436623</v>
       </c>
       <c r="R51" t="n">
-        <v>7027839</v>
+        <v>7027816</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6983,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6993,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7013,6 +6993,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124131669</v>
+        <v>124138449</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436701</v>
+        <v>436602</v>
       </c>
       <c r="R3" t="n">
-        <v>7027783</v>
+        <v>7027958</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +855,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:56</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,51 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124130043</v>
+        <v>124138466</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>91026</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,60 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436564</v>
+        <v>436589</v>
       </c>
       <c r="R4" t="n">
-        <v>7027844</v>
+        <v>7027985</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,21 +962,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,21 +975,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1162,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124130402</v>
+        <v>124131109</v>
       </c>
       <c r="B6" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,46 +1105,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436671</v>
+        <v>436775</v>
       </c>
       <c r="R6" t="n">
-        <v>7027849</v>
+        <v>7027895</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,22 +1197,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138434</v>
+        <v>124138426</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1344,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436588</v>
+        <v>436760</v>
       </c>
       <c r="R7" t="n">
-        <v>7027994</v>
+        <v>7028081</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124134147</v>
+        <v>124130402</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>79927</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,31 +1344,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436555</v>
+        <v>436671</v>
       </c>
       <c r="R8" t="n">
-        <v>7027775</v>
+        <v>7027849</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138449</v>
+        <v>124133243</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,41 +1486,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436602</v>
+        <v>436634</v>
       </c>
       <c r="R9" t="n">
-        <v>7027958</v>
+        <v>7027830</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1621,14 +1552,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,26 +1575,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124138452</v>
+        <v>124126749</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,37 +1632,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436732</v>
+        <v>436643</v>
       </c>
       <c r="R10" t="n">
-        <v>7028026</v>
+        <v>7027739</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,11 +1703,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1741,23 +1731,28 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124127075</v>
+        <v>124132562</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1791,24 +1786,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436458</v>
+        <v>436679</v>
       </c>
       <c r="R11" t="n">
-        <v>7027708</v>
+        <v>7027841</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1847,7 +1837,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,12 +1871,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1899,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138436</v>
+        <v>124131819</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,37 +1910,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436408</v>
+        <v>436725</v>
       </c>
       <c r="R12" t="n">
-        <v>7027885</v>
+        <v>7027833</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1972,11 +1972,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1985,26 +1995,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124131819</v>
+        <v>124130607</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,42 +2052,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436725</v>
+        <v>436700</v>
       </c>
       <c r="R13" t="n">
-        <v>7027833</v>
+        <v>7027918</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2081,7 +2111,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,7 +2121,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,22 +2140,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2143,10 +2173,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124126749</v>
+        <v>124138436</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2159,51 +2189,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436643</v>
+        <v>436408</v>
       </c>
       <c r="R14" t="n">
-        <v>7027739</v>
+        <v>7027885</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2230,26 +2246,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2258,31 +2259,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124130109</v>
+        <v>124129618</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,32 +2291,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2329,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436613</v>
+        <v>436474</v>
       </c>
       <c r="R15" t="n">
-        <v>7027858</v>
+        <v>7027820</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2364,7 +2355,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2374,12 +2365,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,22 +2384,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2431,7 +2417,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138474</v>
+        <v>124138476</v>
       </c>
       <c r="B16" t="n">
         <v>91030</v>
@@ -2471,10 +2457,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436493</v>
+        <v>436556</v>
       </c>
       <c r="R16" t="n">
-        <v>7027911</v>
+        <v>7027990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2533,7 +2519,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138426</v>
+        <v>124138431</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2573,10 +2559,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436760</v>
+        <v>436653</v>
       </c>
       <c r="R17" t="n">
-        <v>7028081</v>
+        <v>7028028</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2635,10 +2621,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138481</v>
+        <v>124138452</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2651,21 +2637,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2675,10 +2661,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436391</v>
+        <v>436732</v>
       </c>
       <c r="R18" t="n">
-        <v>7027787</v>
+        <v>7028026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2737,7 +2723,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138432</v>
+        <v>124138428</v>
       </c>
       <c r="B19" t="n">
         <v>91012</v>
@@ -2777,10 +2763,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436583</v>
+        <v>436678</v>
       </c>
       <c r="R19" t="n">
-        <v>7028008</v>
+        <v>7028031</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2839,10 +2825,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124131109</v>
+        <v>124138423</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,37 +2841,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436775</v>
+        <v>436415</v>
       </c>
       <c r="R20" t="n">
-        <v>7027895</v>
+        <v>7027827</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,21 +2898,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2935,51 +2911,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124134174</v>
+        <v>124130826</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2988,31 +2939,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3021,13 +2972,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436557</v>
+        <v>436743</v>
       </c>
       <c r="R21" t="n">
-        <v>7027773</v>
+        <v>7027889</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3056,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3066,7 +3017,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,22 +3036,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3118,10 +3069,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138431</v>
+        <v>124138453</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3130,25 +3081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3158,10 +3109,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436653</v>
+        <v>436490</v>
       </c>
       <c r="R22" t="n">
-        <v>7028028</v>
+        <v>7027974</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3367,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124134617</v>
+        <v>124131669</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3383,37 +3334,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436450</v>
+        <v>436701</v>
       </c>
       <c r="R24" t="n">
-        <v>7027766</v>
+        <v>7027783</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3442,7 +3398,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3452,12 +3408,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3476,22 +3427,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3509,10 +3460,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124129992</v>
+        <v>124134147</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3525,37 +3476,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436580</v>
+        <v>436555</v>
       </c>
       <c r="R25" t="n">
-        <v>7027853</v>
+        <v>7027775</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3584,7 +3540,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3594,7 +3550,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3613,22 +3569,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3646,10 +3602,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138462</v>
+        <v>124134174</v>
       </c>
       <c r="B26" t="n">
-        <v>91457</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3658,41 +3614,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436591</v>
+        <v>436557</v>
       </c>
       <c r="R26" t="n">
-        <v>7028013</v>
+        <v>7027773</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3719,11 +3680,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3732,26 +3703,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138428</v>
+        <v>124133534</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3764,37 +3760,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436678</v>
+        <v>436627</v>
       </c>
       <c r="R27" t="n">
-        <v>7028031</v>
+        <v>7027780</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3821,11 +3817,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3834,26 +3845,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124133243</v>
+        <v>124134617</v>
       </c>
       <c r="B28" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3862,46 +3898,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436634</v>
+        <v>436450</v>
       </c>
       <c r="R28" t="n">
-        <v>7027830</v>
+        <v>7027766</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3930,7 +3961,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3940,7 +3971,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3959,22 +3995,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3992,10 +4028,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138476</v>
+        <v>124127075</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4008,37 +4044,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436556</v>
+        <v>436458</v>
       </c>
       <c r="R29" t="n">
-        <v>7027990</v>
+        <v>7027708</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4065,11 +4106,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4078,26 +4129,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138453</v>
+        <v>124130487</v>
       </c>
       <c r="B30" t="n">
-        <v>91705</v>
+        <v>57883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4106,41 +4182,60 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436490</v>
+        <v>436684</v>
       </c>
       <c r="R30" t="n">
-        <v>7027974</v>
+        <v>7027902</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4167,11 +4262,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4180,26 +4285,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138423</v>
+        <v>124134565</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4212,34 +4322,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436415</v>
+        <v>436416</v>
       </c>
       <c r="R31" t="n">
-        <v>7027827</v>
+        <v>7027743</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4269,11 +4384,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4282,23 +4412,48 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124132562</v>
+        <v>124129992</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4338,13 +4493,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436679</v>
+        <v>436580</v>
       </c>
       <c r="R32" t="n">
-        <v>7027841</v>
+        <v>7027853</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4373,7 +4528,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4383,12 +4538,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4440,7 +4590,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124130607</v>
+        <v>124131523</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4480,13 +4630,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436700</v>
+        <v>436749</v>
       </c>
       <c r="R33" t="n">
-        <v>7027918</v>
+        <v>7027816</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4515,7 +4665,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4675,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4577,10 +4727,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124131523</v>
+        <v>124138434</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4593,37 +4743,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436749</v>
+        <v>436588</v>
       </c>
       <c r="R34" t="n">
-        <v>7027816</v>
+        <v>7027994</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4650,21 +4800,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4673,51 +4813,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124133665</v>
+        <v>124130731</v>
       </c>
       <c r="B35" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4726,31 +4841,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4759,13 +4883,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436624</v>
+        <v>436707</v>
       </c>
       <c r="R35" t="n">
-        <v>7027776</v>
+        <v>7027946</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4794,7 +4918,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4804,12 +4928,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4824,26 +4943,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4861,10 +4960,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124126979</v>
+        <v>124138478</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4877,42 +4976,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436580</v>
+        <v>436440</v>
       </c>
       <c r="R36" t="n">
-        <v>7027758</v>
+        <v>7027952</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4939,26 +5033,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4967,51 +5046,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124130731</v>
+        <v>124138474</v>
       </c>
       <c r="B37" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5024,48 +5078,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436707</v>
+        <v>436493</v>
       </c>
       <c r="R37" t="n">
-        <v>7027946</v>
+        <v>7027911</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5095,21 +5135,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5118,31 +5148,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124133534</v>
+        <v>124138432</v>
       </c>
       <c r="B38" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5155,37 +5180,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436627</v>
+        <v>436583</v>
       </c>
       <c r="R38" t="n">
-        <v>7027780</v>
+        <v>7028008</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5212,26 +5237,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5240,48 +5250,23 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124129722</v>
+        <v>124129449</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -5321,13 +5306,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436509</v>
+        <v>436417</v>
       </c>
       <c r="R39" t="n">
-        <v>7027814</v>
+        <v>7027793</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5356,7 +5341,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5366,7 +5351,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5418,10 +5403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124130826</v>
+        <v>124133665</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>79926</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5430,31 +5415,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5463,13 +5448,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436743</v>
+        <v>436624</v>
       </c>
       <c r="R40" t="n">
-        <v>7027889</v>
+        <v>7027776</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5498,7 +5483,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5508,7 +5493,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5527,22 +5517,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5560,7 +5550,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124129449</v>
+        <v>124134307</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5596,17 +5586,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436417</v>
+        <v>436504</v>
       </c>
       <c r="R41" t="n">
-        <v>7027793</v>
+        <v>7027727</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5635,7 +5625,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5645,7 +5635,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5697,10 +5687,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124130487</v>
+        <v>124130109</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5709,20 +5699,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5730,19 +5720,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5756,13 +5737,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436684</v>
+        <v>436613</v>
       </c>
       <c r="R42" t="n">
-        <v>7027902</v>
+        <v>7027858</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5791,7 +5772,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5801,7 +5782,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5816,6 +5802,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5833,10 +5839,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138466</v>
+        <v>124129722</v>
       </c>
       <c r="B43" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5849,37 +5855,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436589</v>
+        <v>436509</v>
       </c>
       <c r="R43" t="n">
-        <v>7027985</v>
+        <v>7027814</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5906,11 +5912,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5919,26 +5935,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138478</v>
+        <v>124138481</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5951,21 +5992,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5975,10 +6016,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436440</v>
+        <v>436391</v>
       </c>
       <c r="R44" t="n">
-        <v>7027952</v>
+        <v>7027787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6037,7 +6078,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124134565</v>
+        <v>124126979</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -6078,17 +6119,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R45" t="n">
-        <v>7027743</v>
+        <v>7027758</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6117,7 +6158,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6127,12 +6168,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6161,12 +6202,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6184,10 +6225,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124134307</v>
+        <v>124138462</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6196,41 +6237,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436504</v>
+        <v>436591</v>
       </c>
       <c r="R46" t="n">
-        <v>7027727</v>
+        <v>7028013</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6257,21 +6298,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6280,51 +6311,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124129618</v>
+        <v>124130043</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6333,31 +6339,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6366,13 +6386,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436474</v>
+        <v>436564</v>
       </c>
       <c r="R47" t="n">
-        <v>7027820</v>
+        <v>7027844</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6401,7 +6421,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6411,7 +6431,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6426,26 +6446,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124132300</v>
+        <v>124133343</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6475,40 +6475,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6517,13 +6508,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436689</v>
+        <v>436623</v>
       </c>
       <c r="R48" t="n">
-        <v>7027839</v>
+        <v>7027816</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6552,7 +6543,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6562,12 +6553,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6582,6 +6573,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6599,10 +6610,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124126865</v>
+        <v>124132300</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6611,31 +6622,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6644,10 +6664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436624</v>
+        <v>436689</v>
       </c>
       <c r="R49" t="n">
-        <v>7027776</v>
+        <v>7027839</v>
       </c>
       <c r="S49" t="n">
         <v>11</v>
@@ -6679,7 +6699,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6689,7 +6709,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6704,26 +6729,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6883,10 +6888,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124133343</v>
+        <v>124126865</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6899,27 +6904,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6928,13 +6933,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436623</v>
+        <v>436624</v>
       </c>
       <c r="R51" t="n">
-        <v>7027816</v>
+        <v>7027776</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6968,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6978,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6997,22 +6997,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -2621,10 +2621,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138452</v>
+        <v>124138428</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,21 +2637,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436732</v>
+        <v>436678</v>
       </c>
       <c r="R18" t="n">
-        <v>7028026</v>
+        <v>7028031</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138428</v>
+        <v>124138423</v>
       </c>
       <c r="B19" t="n">
         <v>91012</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436678</v>
+        <v>436415</v>
       </c>
       <c r="R19" t="n">
-        <v>7028031</v>
+        <v>7027827</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138423</v>
+        <v>124138452</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436415</v>
+        <v>436732</v>
       </c>
       <c r="R20" t="n">
-        <v>7027827</v>
+        <v>7028026</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138478</v>
+        <v>124138432</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4976,21 +4976,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436440</v>
+        <v>436583</v>
       </c>
       <c r="R36" t="n">
-        <v>7027952</v>
+        <v>7028008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138474</v>
+        <v>124138478</v>
       </c>
       <c r="B37" t="n">
         <v>91030</v>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436493</v>
+        <v>436440</v>
       </c>
       <c r="R37" t="n">
-        <v>7027911</v>
+        <v>7027952</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138432</v>
+        <v>124133665</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>79926</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5176,41 +5176,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436583</v>
+        <v>436624</v>
       </c>
       <c r="R38" t="n">
-        <v>7028008</v>
+        <v>7027776</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5237,11 +5242,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5250,26 +5270,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124129449</v>
+        <v>124138474</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5282,34 +5327,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436417</v>
+        <v>436493</v>
       </c>
       <c r="R39" t="n">
-        <v>7027793</v>
+        <v>7027911</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5339,21 +5384,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5362,51 +5397,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124133665</v>
+        <v>124129449</v>
       </c>
       <c r="B40" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5415,20 +5425,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5437,24 +5447,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436624</v>
+        <v>436417</v>
       </c>
       <c r="R40" t="n">
-        <v>7027776</v>
+        <v>7027793</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5483,7 +5488,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5493,12 +5498,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5517,22 +5517,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138459</v>
+        <v>124129722</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436448</v>
+        <v>436509</v>
       </c>
       <c r="R2" t="n">
-        <v>7027953</v>
+        <v>7027814</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +748,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,26 +771,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138449</v>
+        <v>124138462</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +824,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436602</v>
+        <v>436591</v>
       </c>
       <c r="R3" t="n">
-        <v>7027958</v>
+        <v>7028013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +888,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138466</v>
+        <v>124130487</v>
       </c>
       <c r="B4" t="n">
-        <v>91026</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +926,60 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436589</v>
+        <v>436684</v>
       </c>
       <c r="R4" t="n">
-        <v>7027985</v>
+        <v>7027902</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,11 +1006,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -975,26 +1029,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138425</v>
+        <v>124138481</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436739</v>
+        <v>436391</v>
       </c>
       <c r="R5" t="n">
-        <v>7028034</v>
+        <v>7027787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124131109</v>
+        <v>124133243</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,41 +1164,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436775</v>
+        <v>436634</v>
       </c>
       <c r="R6" t="n">
-        <v>7027895</v>
+        <v>7027830</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,22 +1261,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138426</v>
+        <v>124134565</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,34 +1310,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436760</v>
+        <v>436416</v>
       </c>
       <c r="R7" t="n">
-        <v>7028081</v>
+        <v>7027743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,11 +1372,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1316,26 +1400,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124130402</v>
+        <v>124130731</v>
       </c>
       <c r="B8" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,31 +1453,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1377,13 +1495,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436671</v>
+        <v>436707</v>
       </c>
       <c r="R8" t="n">
-        <v>7027849</v>
+        <v>7027946</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1530,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1540,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,26 +1555,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1474,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124133243</v>
+        <v>124138428</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,46 +1584,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436634</v>
+        <v>436678</v>
       </c>
       <c r="R9" t="n">
-        <v>7027830</v>
+        <v>7028031</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,21 +1645,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1575,41 +1658,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1752,10 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124132562</v>
+        <v>124138478</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,37 +1826,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436679</v>
+        <v>436440</v>
       </c>
       <c r="R11" t="n">
-        <v>7027841</v>
+        <v>7027952</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1825,26 +1883,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1853,51 +1896,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124131819</v>
+        <v>124138474</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,42 +1928,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436725</v>
+        <v>436493</v>
       </c>
       <c r="R12" t="n">
-        <v>7027833</v>
+        <v>7027911</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1972,21 +1985,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1995,48 +1998,23 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124130607</v>
+        <v>124129449</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2076,13 +2054,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436700</v>
+        <v>436417</v>
       </c>
       <c r="R13" t="n">
-        <v>7027918</v>
+        <v>7027793</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2111,7 +2089,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2121,7 +2099,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2173,10 +2151,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138436</v>
+        <v>124138459</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2189,21 +2167,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2213,10 +2191,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436408</v>
+        <v>436448</v>
       </c>
       <c r="R14" t="n">
-        <v>7027885</v>
+        <v>7027953</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2249,6 +2227,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2275,10 +2258,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124129618</v>
+        <v>124127075</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2291,42 +2274,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436474</v>
+        <v>436458</v>
       </c>
       <c r="R15" t="n">
-        <v>7027820</v>
+        <v>7027708</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2355,7 +2338,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2365,7 +2348,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,22 +2367,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2417,10 +2400,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138476</v>
+        <v>124134617</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,34 +2416,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436556</v>
+        <v>436450</v>
       </c>
       <c r="R16" t="n">
-        <v>7027990</v>
+        <v>7027766</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2490,11 +2473,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2503,23 +2501,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138431</v>
+        <v>124138426</v>
       </c>
       <c r="B17" t="n">
         <v>91012</v>
@@ -2559,10 +2582,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436653</v>
+        <v>436760</v>
       </c>
       <c r="R17" t="n">
-        <v>7028028</v>
+        <v>7028081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2621,7 +2644,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138428</v>
+        <v>124138423</v>
       </c>
       <c r="B18" t="n">
         <v>91012</v>
@@ -2661,10 +2684,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436678</v>
+        <v>436415</v>
       </c>
       <c r="R18" t="n">
-        <v>7028031</v>
+        <v>7027827</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2723,10 +2746,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138423</v>
+        <v>124138449</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,21 +2762,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2763,10 +2786,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436415</v>
+        <v>436602</v>
       </c>
       <c r="R19" t="n">
-        <v>7027827</v>
+        <v>7027958</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2799,6 +2822,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138452</v>
+        <v>124129618</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2841,37 +2869,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436732</v>
+        <v>436474</v>
       </c>
       <c r="R20" t="n">
-        <v>7028026</v>
+        <v>7027820</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2898,11 +2931,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2911,26 +2954,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124130826</v>
+        <v>124131669</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,27 +3011,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2972,13 +3040,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436743</v>
+        <v>436701</v>
       </c>
       <c r="R21" t="n">
-        <v>7027889</v>
+        <v>7027783</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3007,7 +3075,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,7 +3085,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,22 +3104,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3069,10 +3137,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138453</v>
+        <v>124138425</v>
       </c>
       <c r="B22" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3081,25 +3149,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3109,10 +3177,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436490</v>
+        <v>436739</v>
       </c>
       <c r="R22" t="n">
-        <v>7027974</v>
+        <v>7028034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3171,10 +3239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124133629</v>
+        <v>124132562</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3187,42 +3255,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436623</v>
+        <v>436679</v>
       </c>
       <c r="R23" t="n">
-        <v>7027760</v>
+        <v>7027841</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3251,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3261,12 +3324,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3285,22 +3348,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Dead branch  # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3318,10 +3381,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124131669</v>
+        <v>124133665</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>79926</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,25 +3393,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3363,13 +3426,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436701</v>
+        <v>436624</v>
       </c>
       <c r="R24" t="n">
-        <v>7027783</v>
+        <v>7027776</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3398,7 +3461,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3408,7 +3471,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3437,12 +3505,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3460,10 +3528,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124134147</v>
+        <v>124133629</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3476,21 +3544,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3505,13 +3573,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436555</v>
+        <v>436623</v>
       </c>
       <c r="R25" t="n">
-        <v>7027775</v>
+        <v>7027760</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3540,7 +3608,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3550,7 +3618,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3579,12 +3652,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3602,10 +3675,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124134174</v>
+        <v>124130402</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>79927</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3618,21 +3691,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3647,13 +3720,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436557</v>
+        <v>436671</v>
       </c>
       <c r="R26" t="n">
-        <v>7027773</v>
+        <v>7027849</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3682,7 +3755,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3692,7 +3765,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3744,10 +3817,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124133534</v>
+        <v>124126979</v>
       </c>
       <c r="B27" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3760,37 +3833,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436627</v>
+        <v>436580</v>
       </c>
       <c r="R27" t="n">
-        <v>7027780</v>
+        <v>7027758</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3819,7 +3897,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3829,12 +3907,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3853,22 +3931,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3886,7 +3964,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124134617</v>
+        <v>124130607</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3926,13 +4004,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436450</v>
+        <v>436700</v>
       </c>
       <c r="R28" t="n">
-        <v>7027766</v>
+        <v>7027918</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3961,7 +4039,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3971,12 +4049,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4028,7 +4101,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124127075</v>
+        <v>124134307</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -4062,24 +4135,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436458</v>
+        <v>436504</v>
       </c>
       <c r="R29" t="n">
-        <v>7027708</v>
+        <v>7027727</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4108,7 +4176,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4118,7 +4186,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4147,12 +4215,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4170,7 +4238,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124130487</v>
+        <v>124130043</v>
       </c>
       <c r="B30" t="n">
         <v>57883</v>
@@ -4229,10 +4297,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436684</v>
+        <v>436564</v>
       </c>
       <c r="R30" t="n">
-        <v>7027902</v>
+        <v>7027844</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4264,7 +4332,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4342,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4306,10 +4374,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124134565</v>
+        <v>124129992</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4322,42 +4390,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R31" t="n">
-        <v>7027743</v>
+        <v>7027853</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4386,7 +4449,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4396,12 +4459,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4430,12 +4488,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4453,10 +4511,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124129992</v>
+        <v>124138432</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4469,37 +4527,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436580</v>
+        <v>436583</v>
       </c>
       <c r="R32" t="n">
-        <v>7027853</v>
+        <v>7028008</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4526,21 +4584,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4549,51 +4597,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124131523</v>
+        <v>124133534</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4606,21 +4629,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4630,13 +4653,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436749</v>
+        <v>436627</v>
       </c>
       <c r="R33" t="n">
-        <v>7027816</v>
+        <v>7027780</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4665,7 +4688,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4675,7 +4698,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4694,22 +4722,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4727,10 +4755,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138434</v>
+        <v>124130109</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4743,37 +4771,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436588</v>
+        <v>436613</v>
       </c>
       <c r="R34" t="n">
-        <v>7027994</v>
+        <v>7027858</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4800,11 +4838,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4813,26 +4866,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124130731</v>
+        <v>124134174</v>
       </c>
       <c r="B35" t="n">
-        <v>56714</v>
+        <v>79920</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4841,40 +4919,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4883,13 +4952,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436707</v>
+        <v>436557</v>
       </c>
       <c r="R35" t="n">
-        <v>7027946</v>
+        <v>7027773</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4918,7 +4987,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4928,7 +4997,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4943,6 +5012,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4960,10 +5049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138432</v>
+        <v>124131819</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4976,37 +5065,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436583</v>
+        <v>436725</v>
       </c>
       <c r="R36" t="n">
-        <v>7028008</v>
+        <v>7027833</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5033,11 +5127,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5046,26 +5150,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138478</v>
+        <v>124138431</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5078,21 +5207,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5102,10 +5231,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436440</v>
+        <v>436653</v>
       </c>
       <c r="R37" t="n">
-        <v>7027952</v>
+        <v>7028028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5164,10 +5293,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124133665</v>
+        <v>124138453</v>
       </c>
       <c r="B38" t="n">
-        <v>79926</v>
+        <v>91705</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5176,46 +5305,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>67</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436624</v>
+        <v>436490</v>
       </c>
       <c r="R38" t="n">
-        <v>7027776</v>
+        <v>7027974</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5242,26 +5366,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5270,51 +5379,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138474</v>
+        <v>124131109</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5327,37 +5411,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436493</v>
+        <v>436775</v>
       </c>
       <c r="R39" t="n">
-        <v>7027911</v>
+        <v>7027895</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5384,11 +5468,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5397,26 +5491,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124129449</v>
+        <v>124130826</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5429,37 +5548,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436417</v>
+        <v>436743</v>
       </c>
       <c r="R40" t="n">
-        <v>7027793</v>
+        <v>7027889</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5488,7 +5612,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5498,7 +5622,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5527,12 +5651,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5550,10 +5674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124134307</v>
+        <v>124138436</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5566,37 +5690,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436504</v>
+        <v>436408</v>
       </c>
       <c r="R41" t="n">
-        <v>7027727</v>
+        <v>7027885</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5623,21 +5747,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5646,51 +5760,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124130109</v>
+        <v>124134147</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>79892</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5703,32 +5792,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5737,13 +5821,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436613</v>
+        <v>436555</v>
       </c>
       <c r="R42" t="n">
-        <v>7027858</v>
+        <v>7027775</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5772,7 +5856,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5782,12 +5866,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5806,22 +5885,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5839,10 +5918,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124129722</v>
+        <v>124138452</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5855,37 +5934,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436509</v>
+        <v>436732</v>
       </c>
       <c r="R43" t="n">
-        <v>7027814</v>
+        <v>7028026</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5912,21 +5991,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5935,51 +6004,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138481</v>
+        <v>124138476</v>
       </c>
       <c r="B44" t="n">
-        <v>88359</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5992,21 +6036,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6016,10 +6060,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436391</v>
+        <v>436556</v>
       </c>
       <c r="R44" t="n">
-        <v>7027787</v>
+        <v>7027990</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6078,10 +6122,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124126979</v>
+        <v>124138434</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6094,42 +6138,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436580</v>
+        <v>436588</v>
       </c>
       <c r="R45" t="n">
-        <v>7027758</v>
+        <v>7027994</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6156,26 +6195,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6184,51 +6208,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138462</v>
+        <v>124138466</v>
       </c>
       <c r="B46" t="n">
-        <v>91457</v>
+        <v>91026</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6237,25 +6236,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6265,10 +6264,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436591</v>
+        <v>436589</v>
       </c>
       <c r="R46" t="n">
-        <v>7028013</v>
+        <v>7027985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6327,10 +6326,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124130043</v>
+        <v>124131523</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6339,60 +6338,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436564</v>
+        <v>436749</v>
       </c>
       <c r="R47" t="n">
-        <v>7027844</v>
+        <v>7027816</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6421,7 +6401,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6431,7 +6411,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6446,6 +6426,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124133343</v>
+        <v>124132300</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6475,31 +6475,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6508,13 +6517,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436623</v>
+        <v>436689</v>
       </c>
       <c r="R48" t="n">
-        <v>7027816</v>
+        <v>7027839</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6543,7 +6552,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6553,12 +6562,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6573,26 +6582,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6610,10 +6599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124132300</v>
+        <v>124126865</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6622,40 +6611,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6664,10 +6644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436689</v>
+        <v>436624</v>
       </c>
       <c r="R49" t="n">
-        <v>7027839</v>
+        <v>7027776</v>
       </c>
       <c r="S49" t="n">
         <v>11</v>
@@ -6699,7 +6679,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6709,12 +6689,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6729,6 +6704,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6888,10 +6883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124126865</v>
+        <v>124133343</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6904,27 +6899,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6933,13 +6928,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436624</v>
+        <v>436623</v>
       </c>
       <c r="R51" t="n">
-        <v>7027776</v>
+        <v>7027816</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6968,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6978,7 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6997,22 +6997,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -2400,10 +2400,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124134617</v>
+        <v>124138426</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436450</v>
+        <v>436760</v>
       </c>
       <c r="R16" t="n">
-        <v>7027766</v>
+        <v>7028081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,26 +2473,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2501,51 +2486,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138426</v>
+        <v>124134617</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2558,34 +2518,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436760</v>
+        <v>436450</v>
       </c>
       <c r="R17" t="n">
-        <v>7028081</v>
+        <v>7027766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2615,11 +2575,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2628,16 +2603,41 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138425</v>
+        <v>124126979</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3153,37 +3153,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436739</v>
+        <v>436580</v>
       </c>
       <c r="R22" t="n">
-        <v>7028034</v>
+        <v>7027758</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3210,11 +3215,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3223,16 +3243,41 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3817,10 +3862,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124126979</v>
+        <v>124138425</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3833,42 +3878,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436580</v>
+        <v>436739</v>
       </c>
       <c r="R27" t="n">
-        <v>7027758</v>
+        <v>7028034</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3895,26 +3935,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3923,41 +3948,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124129722</v>
+        <v>124138462</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436509</v>
+        <v>436591</v>
       </c>
       <c r="R2" t="n">
-        <v>7027814</v>
+        <v>7028013</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +748,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138462</v>
+        <v>124129722</v>
       </c>
       <c r="B3" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436591</v>
+        <v>436509</v>
       </c>
       <c r="R3" t="n">
-        <v>7028013</v>
+        <v>7027814</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +850,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,16 +873,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6122,10 +6122,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138434</v>
+        <v>124131523</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6138,37 +6138,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436588</v>
+        <v>436749</v>
       </c>
       <c r="R45" t="n">
-        <v>7027994</v>
+        <v>7027816</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6195,11 +6195,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6208,26 +6218,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138466</v>
+        <v>124138434</v>
       </c>
       <c r="B46" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6240,21 +6275,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6264,10 +6299,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436589</v>
+        <v>436588</v>
       </c>
       <c r="R46" t="n">
-        <v>7027985</v>
+        <v>7027994</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6326,10 +6361,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124131523</v>
+        <v>124138466</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6342,37 +6377,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436749</v>
+        <v>436589</v>
       </c>
       <c r="R47" t="n">
-        <v>7027816</v>
+        <v>7027985</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6399,21 +6434,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6422,41 +6447,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138462</v>
+        <v>124138478</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436591</v>
+        <v>436440</v>
       </c>
       <c r="R2" t="n">
-        <v>7028013</v>
+        <v>7027952</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124129722</v>
+        <v>124130826</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436509</v>
+        <v>436743</v>
       </c>
       <c r="R3" t="n">
-        <v>7027814</v>
+        <v>7027889</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +896,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124130487</v>
+        <v>124134617</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,60 +931,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436684</v>
+        <v>436450</v>
       </c>
       <c r="R4" t="n">
-        <v>7027902</v>
+        <v>7027766</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,6 +1024,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138481</v>
+        <v>124138434</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1077,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436391</v>
+        <v>436588</v>
       </c>
       <c r="R5" t="n">
-        <v>7027787</v>
+        <v>7027994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124133243</v>
+        <v>124138452</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,46 +1175,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436634</v>
+        <v>436732</v>
       </c>
       <c r="R6" t="n">
-        <v>7027830</v>
+        <v>7028026</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,21 +1236,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1253,73 +1249,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124134565</v>
+        <v>124130487</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1327,25 +1298,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436416</v>
+        <v>436684</v>
       </c>
       <c r="R7" t="n">
-        <v>7027743</v>
+        <v>7027902</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,12 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,26 +1384,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1441,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124130731</v>
+        <v>124132562</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,51 +1417,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436707</v>
+        <v>436679</v>
       </c>
       <c r="R8" t="n">
-        <v>7027946</v>
+        <v>7027841</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1530,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1540,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,6 +1506,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1572,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138428</v>
+        <v>124138481</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1588,21 +1559,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1583,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436678</v>
+        <v>436391</v>
       </c>
       <c r="R9" t="n">
-        <v>7028031</v>
+        <v>7027787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124126749</v>
+        <v>124130109</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,31 +1661,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1728,13 +1695,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436643</v>
+        <v>436613</v>
       </c>
       <c r="R10" t="n">
-        <v>7027739</v>
+        <v>7027858</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1763,7 +1730,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1773,12 +1740,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,6 +1760,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1810,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138478</v>
+        <v>124129618</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1826,37 +1813,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436440</v>
+        <v>436474</v>
       </c>
       <c r="R11" t="n">
-        <v>7027952</v>
+        <v>7027820</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1883,11 +1875,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1896,26 +1898,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138474</v>
+        <v>124129449</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,34 +1955,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436493</v>
+        <v>436417</v>
       </c>
       <c r="R12" t="n">
-        <v>7027911</v>
+        <v>7027793</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1985,11 +2012,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1998,26 +2035,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124129449</v>
+        <v>124138436</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,34 +2092,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436417</v>
+        <v>436408</v>
       </c>
       <c r="R13" t="n">
-        <v>7027793</v>
+        <v>7027885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,21 +2149,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2110,51 +2162,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138459</v>
+        <v>124130043</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,20 +2190,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2184,20 +2211,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436448</v>
+        <v>436564</v>
       </c>
       <c r="R14" t="n">
-        <v>7027953</v>
+        <v>7027844</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2224,14 +2270,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,26 +2293,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124127075</v>
+        <v>124134174</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2270,25 +2326,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,17 +2355,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436458</v>
+        <v>436557</v>
       </c>
       <c r="R15" t="n">
-        <v>7027708</v>
+        <v>7027773</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2338,7 +2394,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2348,7 +2404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2367,22 +2423,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2400,10 +2456,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138426</v>
+        <v>124138466</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91026</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2416,21 +2472,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2440,10 +2496,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436760</v>
+        <v>436589</v>
       </c>
       <c r="R16" t="n">
-        <v>7028081</v>
+        <v>7027985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,10 +2558,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124134617</v>
+        <v>124133629</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2518,37 +2574,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436450</v>
+        <v>436623</v>
       </c>
       <c r="R17" t="n">
-        <v>7027766</v>
+        <v>7027760</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2577,7 +2638,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2587,12 +2648,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2611,22 +2672,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2644,10 +2705,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138423</v>
+        <v>124126749</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2660,37 +2721,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436415</v>
+        <v>436643</v>
       </c>
       <c r="R18" t="n">
-        <v>7027827</v>
+        <v>7027739</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2717,11 +2792,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2730,30 +2820,35 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138449</v>
+        <v>124138432</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2762,21 +2857,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2786,10 +2881,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436602</v>
+        <v>436583</v>
       </c>
       <c r="R19" t="n">
-        <v>7027958</v>
+        <v>7028008</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2822,11 +2917,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2853,7 +2943,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124129618</v>
+        <v>124131669</v>
       </c>
       <c r="B20" t="n">
         <v>79891</v>
@@ -2898,10 +2988,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436474</v>
+        <v>436701</v>
       </c>
       <c r="R20" t="n">
-        <v>7027820</v>
+        <v>7027783</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2933,7 +3023,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2943,7 +3033,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2995,10 +3085,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124131669</v>
+        <v>124129722</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3011,42 +3101,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436701</v>
+        <v>436509</v>
       </c>
       <c r="R21" t="n">
-        <v>7027783</v>
+        <v>7027814</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3075,7 +3160,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3085,7 +3170,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3104,22 +3189,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3137,58 +3222,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124126979</v>
+        <v>124138453</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436580</v>
+        <v>436490</v>
       </c>
       <c r="R22" t="n">
-        <v>7027758</v>
+        <v>7027974</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3215,26 +3295,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3243,51 +3308,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124132562</v>
+        <v>124138474</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3300,37 +3340,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436679</v>
+        <v>436493</v>
       </c>
       <c r="R23" t="n">
-        <v>7027841</v>
+        <v>7027911</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3357,26 +3397,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3385,51 +3410,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124133665</v>
+        <v>124131523</v>
       </c>
       <c r="B24" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3438,20 +3438,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3460,24 +3460,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436624</v>
+        <v>436749</v>
       </c>
       <c r="R24" t="n">
-        <v>7027776</v>
+        <v>7027816</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3506,7 +3501,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3516,12 +3511,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3540,22 +3530,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3573,10 +3563,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124133629</v>
+        <v>124138476</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3589,42 +3579,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436623</v>
+        <v>436556</v>
       </c>
       <c r="R25" t="n">
-        <v>7027760</v>
+        <v>7027990</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3651,26 +3636,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3679,51 +3649,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124130402</v>
+        <v>124138462</v>
       </c>
       <c r="B26" t="n">
-        <v>79927</v>
+        <v>91457</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3732,46 +3677,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436671</v>
+        <v>436591</v>
       </c>
       <c r="R26" t="n">
-        <v>7027849</v>
+        <v>7028013</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3798,21 +3738,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3821,51 +3751,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138425</v>
+        <v>124138459</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3878,21 +3783,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3902,10 +3807,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436739</v>
+        <v>436448</v>
       </c>
       <c r="R27" t="n">
-        <v>7028034</v>
+        <v>7027953</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3938,6 +3843,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3964,10 +3874,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124130607</v>
+        <v>124133243</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3976,41 +3886,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436700</v>
+        <v>436634</v>
       </c>
       <c r="R28" t="n">
-        <v>7027918</v>
+        <v>7027830</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4039,7 +3954,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4049,7 +3964,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4068,22 +3983,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4101,10 +4016,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124134307</v>
+        <v>124134147</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4117,37 +4032,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436504</v>
+        <v>436555</v>
       </c>
       <c r="R29" t="n">
-        <v>7027727</v>
+        <v>7027775</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4176,7 +4096,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4186,7 +4106,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4205,22 +4125,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4238,10 +4158,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124130043</v>
+        <v>124133534</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4250,60 +4170,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436564</v>
+        <v>436627</v>
       </c>
       <c r="R30" t="n">
-        <v>7027844</v>
+        <v>7027780</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4332,7 +4233,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4342,7 +4243,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4357,6 +4263,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4374,7 +4300,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124129992</v>
+        <v>124134307</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -4410,14 +4336,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436580</v>
+        <v>436504</v>
       </c>
       <c r="R31" t="n">
-        <v>7027853</v>
+        <v>7027727</v>
       </c>
       <c r="S31" t="n">
         <v>11</v>
@@ -4449,7 +4375,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4459,7 +4385,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4511,7 +4437,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138432</v>
+        <v>124138428</v>
       </c>
       <c r="B32" t="n">
         <v>91012</v>
@@ -4551,10 +4477,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436583</v>
+        <v>436678</v>
       </c>
       <c r="R32" t="n">
-        <v>7028008</v>
+        <v>7028031</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4613,10 +4539,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124133534</v>
+        <v>124138425</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4629,37 +4555,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436627</v>
+        <v>436739</v>
       </c>
       <c r="R33" t="n">
-        <v>7027780</v>
+        <v>7028034</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4686,26 +4612,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4714,51 +4625,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124130109</v>
+        <v>124138426</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4771,47 +4657,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436613</v>
+        <v>436760</v>
       </c>
       <c r="R34" t="n">
-        <v>7027858</v>
+        <v>7028081</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4838,26 +4714,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4866,51 +4727,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124134174</v>
+        <v>124133665</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4923,27 +4759,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4952,10 +4788,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436557</v>
+        <v>436624</v>
       </c>
       <c r="R35" t="n">
-        <v>7027773</v>
+        <v>7027776</v>
       </c>
       <c r="S35" t="n">
         <v>12</v>
@@ -4987,7 +4823,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4997,7 +4833,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5026,12 +4867,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5049,10 +4890,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124131819</v>
+        <v>124138423</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5065,42 +4906,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436725</v>
+        <v>436415</v>
       </c>
       <c r="R36" t="n">
-        <v>7027833</v>
+        <v>7027827</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5127,21 +4963,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5150,51 +4976,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138431</v>
+        <v>124130731</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5207,34 +5008,48 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436653</v>
+        <v>436707</v>
       </c>
       <c r="R37" t="n">
-        <v>7028028</v>
+        <v>7027946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5264,11 +5079,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5277,26 +5102,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138453</v>
+        <v>124130607</v>
       </c>
       <c r="B38" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5305,41 +5135,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436490</v>
+        <v>436700</v>
       </c>
       <c r="R38" t="n">
-        <v>7027974</v>
+        <v>7027918</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5366,11 +5196,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5379,26 +5219,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124131109</v>
+        <v>124131819</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5411,34 +5276,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436775</v>
+        <v>436725</v>
       </c>
       <c r="R39" t="n">
-        <v>7027895</v>
+        <v>7027833</v>
       </c>
       <c r="S39" t="n">
         <v>7</v>
@@ -5470,7 +5340,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5480,7 +5350,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5499,22 +5369,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5532,10 +5402,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124130826</v>
+        <v>124131109</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5548,42 +5418,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436743</v>
+        <v>436775</v>
       </c>
       <c r="R40" t="n">
-        <v>7027889</v>
+        <v>7027895</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5612,7 +5477,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5622,7 +5487,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5651,12 +5516,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5674,7 +5539,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138436</v>
+        <v>124138431</v>
       </c>
       <c r="B41" t="n">
         <v>91012</v>
@@ -5714,10 +5579,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436408</v>
+        <v>436653</v>
       </c>
       <c r="R41" t="n">
-        <v>7027885</v>
+        <v>7028028</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5776,10 +5641,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124134147</v>
+        <v>124129992</v>
       </c>
       <c r="B42" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5792,42 +5657,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436555</v>
+        <v>436580</v>
       </c>
       <c r="R42" t="n">
-        <v>7027775</v>
+        <v>7027853</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5856,7 +5716,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5866,7 +5726,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5885,22 +5745,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5918,10 +5778,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138452</v>
+        <v>124127075</v>
       </c>
       <c r="B43" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5934,37 +5794,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436732</v>
+        <v>436458</v>
       </c>
       <c r="R43" t="n">
-        <v>7028026</v>
+        <v>7027708</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5991,11 +5856,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6004,26 +5879,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138476</v>
+        <v>124130402</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>79927</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6032,41 +5932,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436556</v>
+        <v>436671</v>
       </c>
       <c r="R44" t="n">
-        <v>7027990</v>
+        <v>7027849</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6093,11 +5998,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6106,26 +6021,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124131523</v>
+        <v>124133039</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6138,34 +6078,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436749</v>
+        <v>436650</v>
       </c>
       <c r="R45" t="n">
-        <v>7027816</v>
+        <v>7027809</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -6197,7 +6142,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6207,7 +6152,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6236,12 +6181,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6259,10 +6204,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138434</v>
+        <v>124132300</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6271,41 +6216,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436588</v>
+        <v>436689</v>
       </c>
       <c r="R46" t="n">
-        <v>7027994</v>
+        <v>7027839</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6332,11 +6291,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6345,26 +6319,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138466</v>
+        <v>124133343</v>
       </c>
       <c r="B47" t="n">
-        <v>91026</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6377,37 +6356,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436589</v>
+        <v>436623</v>
       </c>
       <c r="R47" t="n">
-        <v>7027985</v>
+        <v>7027816</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6434,11 +6418,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6447,26 +6446,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124132300</v>
+        <v>124126865</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6475,40 +6499,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6517,10 +6532,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436689</v>
+        <v>436624</v>
       </c>
       <c r="R48" t="n">
-        <v>7027839</v>
+        <v>7027776</v>
       </c>
       <c r="S48" t="n">
         <v>11</v>
@@ -6552,7 +6567,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6562,12 +6577,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6582,6 +6592,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6599,14 +6629,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124126865</v>
+        <v>124138449</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6615,42 +6645,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436624</v>
+        <v>436602</v>
       </c>
       <c r="R49" t="n">
-        <v>7027776</v>
+        <v>7027958</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6677,19 +6702,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:11</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6700,55 +6720,30 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124133039</v>
+        <v>124126979</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6757,27 +6752,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6786,13 +6781,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436650</v>
+        <v>436580</v>
       </c>
       <c r="R50" t="n">
-        <v>7027809</v>
+        <v>7027758</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6821,7 +6816,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6831,7 +6826,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6883,14 +6883,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124133343</v>
+        <v>124134565</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6899,42 +6899,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436623</v>
+        <v>436416</v>
       </c>
       <c r="R51" t="n">
-        <v>7027816</v>
+        <v>7027743</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6997,22 +6997,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138478</v>
+        <v>124138425</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436440</v>
+        <v>436739</v>
       </c>
       <c r="R2" t="n">
-        <v>7027952</v>
+        <v>7028034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124130826</v>
+        <v>124133243</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,31 +789,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436743</v>
+        <v>436634</v>
       </c>
       <c r="R3" t="n">
-        <v>7027889</v>
+        <v>7027830</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +886,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124134617</v>
+        <v>124138426</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436450</v>
+        <v>436760</v>
       </c>
       <c r="R4" t="n">
-        <v>7027766</v>
+        <v>7028081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,26 +992,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,51 +1005,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138434</v>
+        <v>124130043</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,41 +1033,60 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436588</v>
+        <v>436564</v>
       </c>
       <c r="R5" t="n">
-        <v>7027994</v>
+        <v>7027844</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,11 +1113,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1147,26 +1136,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138452</v>
+        <v>124134307</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,37 +1173,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436732</v>
+        <v>436504</v>
       </c>
       <c r="R6" t="n">
-        <v>7028026</v>
+        <v>7027727</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,11 +1230,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1249,26 +1253,51 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124130487</v>
+        <v>124127075</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,60 +1306,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436684</v>
+        <v>436458</v>
       </c>
       <c r="R7" t="n">
-        <v>7027902</v>
+        <v>7027708</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1374,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,6 +1399,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1401,7 +1436,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124132562</v>
+        <v>124129449</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1441,13 +1476,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436679</v>
+        <v>436417</v>
       </c>
       <c r="R8" t="n">
-        <v>7027841</v>
+        <v>7027793</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1511,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1521,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138481</v>
+        <v>124138423</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,21 +1589,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1583,10 +1613,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436391</v>
+        <v>436415</v>
       </c>
       <c r="R9" t="n">
-        <v>7027787</v>
+        <v>7027827</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124130109</v>
+        <v>124129618</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,32 +1691,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1695,13 +1720,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436613</v>
+        <v>436474</v>
       </c>
       <c r="R10" t="n">
-        <v>7027858</v>
+        <v>7027820</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,7 +1755,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,12 +1765,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,22 +1784,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1797,10 +1817,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124129618</v>
+        <v>124134147</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1813,21 +1833,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,13 +1862,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436474</v>
+        <v>436555</v>
       </c>
       <c r="R11" t="n">
-        <v>7027820</v>
+        <v>7027775</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1877,7 +1897,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1887,7 +1907,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1939,10 +1959,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124129449</v>
+        <v>124138453</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1951,38 +1971,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436417</v>
+        <v>436490</v>
       </c>
       <c r="R12" t="n">
-        <v>7027793</v>
+        <v>7027974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2012,21 +2032,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2035,51 +2045,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124138436</v>
+        <v>124138452</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,21 +2077,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2116,10 +2101,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436408</v>
+        <v>436732</v>
       </c>
       <c r="R13" t="n">
-        <v>7027885</v>
+        <v>7028026</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2178,10 +2163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124130043</v>
+        <v>124138434</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2190,60 +2175,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436564</v>
+        <v>436588</v>
       </c>
       <c r="R14" t="n">
-        <v>7027844</v>
+        <v>7027994</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2270,21 +2236,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2293,31 +2249,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124134174</v>
+        <v>124138476</v>
       </c>
       <c r="B15" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2326,46 +2277,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436557</v>
+        <v>436556</v>
       </c>
       <c r="R15" t="n">
-        <v>7027773</v>
+        <v>7027990</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,21 +2338,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2415,51 +2351,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138466</v>
+        <v>124126749</v>
       </c>
       <c r="B16" t="n">
-        <v>91026</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2472,37 +2383,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436589</v>
+        <v>436643</v>
       </c>
       <c r="R16" t="n">
-        <v>7027985</v>
+        <v>7027739</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2529,11 +2454,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2542,26 +2482,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124133629</v>
+        <v>124138481</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>88359</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2574,42 +2519,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436623</v>
+        <v>436391</v>
       </c>
       <c r="R17" t="n">
-        <v>7027760</v>
+        <v>7027787</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2636,26 +2576,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2664,51 +2589,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Dead branch  # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124126749</v>
+        <v>124132562</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2721,51 +2621,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436643</v>
+        <v>436679</v>
       </c>
       <c r="R18" t="n">
-        <v>7027739</v>
+        <v>7027841</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2794,7 +2680,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2804,12 +2690,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2824,6 +2710,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2841,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138432</v>
+        <v>124129722</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2857,37 +2763,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436583</v>
+        <v>436509</v>
       </c>
       <c r="R19" t="n">
-        <v>7028008</v>
+        <v>7027814</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2914,11 +2820,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2927,26 +2843,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124131669</v>
+        <v>124130607</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2959,42 +2900,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436701</v>
+        <v>436700</v>
       </c>
       <c r="R20" t="n">
-        <v>7027783</v>
+        <v>7027918</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3023,7 +2959,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3033,7 +2969,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3052,22 +2988,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3085,10 +3021,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124129722</v>
+        <v>124134174</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3097,41 +3033,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436509</v>
+        <v>436557</v>
       </c>
       <c r="R21" t="n">
-        <v>7027814</v>
+        <v>7027773</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3160,7 +3101,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3170,7 +3111,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3189,22 +3130,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3222,10 +3163,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138453</v>
+        <v>124131523</v>
       </c>
       <c r="B22" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3234,41 +3175,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436490</v>
+        <v>436749</v>
       </c>
       <c r="R22" t="n">
-        <v>7027974</v>
+        <v>7027816</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3295,11 +3236,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3308,26 +3259,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138474</v>
+        <v>124130109</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3340,37 +3316,47 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436493</v>
+        <v>436613</v>
       </c>
       <c r="R23" t="n">
-        <v>7027911</v>
+        <v>7027858</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3397,11 +3383,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3410,26 +3411,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124131523</v>
+        <v>124130826</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3442,37 +3468,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436749</v>
+        <v>436743</v>
       </c>
       <c r="R24" t="n">
-        <v>7027816</v>
+        <v>7027889</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3501,7 +3532,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3511,7 +3542,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3540,12 +3571,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3563,10 +3594,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138476</v>
+        <v>124130487</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3575,41 +3606,60 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436556</v>
+        <v>436684</v>
       </c>
       <c r="R25" t="n">
-        <v>7027990</v>
+        <v>7027902</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3636,11 +3686,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3649,26 +3709,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138462</v>
+        <v>124138432</v>
       </c>
       <c r="B26" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3677,25 +3742,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3705,10 +3770,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436591</v>
+        <v>436583</v>
       </c>
       <c r="R26" t="n">
-        <v>7028013</v>
+        <v>7028008</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3767,10 +3832,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138459</v>
+        <v>124138478</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3783,21 +3848,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3807,10 +3872,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436448</v>
+        <v>436440</v>
       </c>
       <c r="R27" t="n">
-        <v>7027953</v>
+        <v>7027952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3843,11 +3908,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3874,10 +3934,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124133243</v>
+        <v>124138436</v>
       </c>
       <c r="B28" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3886,46 +3946,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436634</v>
+        <v>436408</v>
       </c>
       <c r="R28" t="n">
-        <v>7027830</v>
+        <v>7027885</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3952,21 +4007,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3975,51 +4020,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124134147</v>
+        <v>124133629</v>
       </c>
       <c r="B29" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4032,21 +4052,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4061,13 +4081,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436555</v>
+        <v>436623</v>
       </c>
       <c r="R29" t="n">
-        <v>7027775</v>
+        <v>7027760</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4096,7 +4116,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4106,7 +4126,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4135,12 +4160,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4158,10 +4183,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124133534</v>
+        <v>124138462</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>91457</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4170,41 +4195,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436627</v>
+        <v>436591</v>
       </c>
       <c r="R30" t="n">
-        <v>7027780</v>
+        <v>7028013</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4231,26 +4256,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4259,51 +4269,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124134307</v>
+        <v>124138474</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4316,37 +4301,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436504</v>
+        <v>436493</v>
       </c>
       <c r="R31" t="n">
-        <v>7027727</v>
+        <v>7027911</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4373,21 +4358,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4396,51 +4371,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138428</v>
+        <v>124131109</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4453,37 +4403,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436678</v>
+        <v>436775</v>
       </c>
       <c r="R32" t="n">
-        <v>7028031</v>
+        <v>7027895</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4510,11 +4460,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4523,26 +4483,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138425</v>
+        <v>124134617</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4555,34 +4540,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436739</v>
+        <v>436450</v>
       </c>
       <c r="R33" t="n">
-        <v>7028034</v>
+        <v>7027766</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,11 +4597,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4625,26 +4625,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138426</v>
+        <v>124130731</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4657,34 +4682,48 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436760</v>
+        <v>436707</v>
       </c>
       <c r="R34" t="n">
-        <v>7028081</v>
+        <v>7027946</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4714,11 +4753,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4727,26 +4776,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124133665</v>
+        <v>124138431</v>
       </c>
       <c r="B35" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4755,46 +4809,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436624</v>
+        <v>436653</v>
       </c>
       <c r="R35" t="n">
-        <v>7027776</v>
+        <v>7028028</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4821,26 +4870,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4849,51 +4883,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138423</v>
+        <v>124129992</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4906,37 +4915,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436415</v>
+        <v>436580</v>
       </c>
       <c r="R36" t="n">
-        <v>7027827</v>
+        <v>7027853</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4963,11 +4972,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4976,26 +4995,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124130731</v>
+        <v>124130402</v>
       </c>
       <c r="B37" t="n">
-        <v>56714</v>
+        <v>79927</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5004,40 +5048,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5046,13 +5081,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436707</v>
+        <v>436671</v>
       </c>
       <c r="R37" t="n">
-        <v>7027946</v>
+        <v>7027849</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5081,7 +5116,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5091,7 +5126,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5106,6 +5141,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5123,10 +5178,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124130607</v>
+        <v>124138466</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5139,37 +5194,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436700</v>
+        <v>436589</v>
       </c>
       <c r="R38" t="n">
-        <v>7027918</v>
+        <v>7027985</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5196,21 +5251,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5219,51 +5264,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124131819</v>
+        <v>124138428</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5276,42 +5296,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436725</v>
+        <v>436678</v>
       </c>
       <c r="R39" t="n">
-        <v>7027833</v>
+        <v>7028031</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5338,21 +5353,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5361,51 +5366,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124131109</v>
+        <v>124131819</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5418,34 +5398,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436775</v>
+        <v>436725</v>
       </c>
       <c r="R40" t="n">
-        <v>7027895</v>
+        <v>7027833</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
@@ -5477,7 +5462,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5487,7 +5472,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5506,22 +5491,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5539,10 +5524,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138431</v>
+        <v>124131669</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5555,37 +5540,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436653</v>
+        <v>436701</v>
       </c>
       <c r="R41" t="n">
-        <v>7028028</v>
+        <v>7027783</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5612,11 +5602,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5625,26 +5625,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124129992</v>
+        <v>124138459</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5657,37 +5682,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436580</v>
+        <v>436448</v>
       </c>
       <c r="R42" t="n">
-        <v>7027853</v>
+        <v>7027953</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5714,19 +5739,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:51</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5737,51 +5757,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124127075</v>
+        <v>124133665</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5790,20 +5785,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5814,22 +5809,22 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436458</v>
+        <v>436624</v>
       </c>
       <c r="R43" t="n">
-        <v>7027708</v>
+        <v>7027776</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5858,7 +5853,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5868,7 +5863,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,22 +5887,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124130402</v>
+        <v>124133534</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>79892</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5932,46 +5932,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436671</v>
+        <v>436627</v>
       </c>
       <c r="R44" t="n">
-        <v>7027849</v>
+        <v>7027780</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6000,7 +5995,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6010,7 +6005,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124133039</v>
+        <v>124133343</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6078,27 +6078,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6107,13 +6107,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436650</v>
+        <v>436623</v>
       </c>
       <c r="R45" t="n">
-        <v>7027809</v>
+        <v>7027816</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6152,7 +6152,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6171,22 +6176,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6204,10 +6209,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124132300</v>
+        <v>124133039</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6216,40 +6221,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6258,13 +6254,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436689</v>
+        <v>436650</v>
       </c>
       <c r="R46" t="n">
-        <v>7027839</v>
+        <v>7027809</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6293,7 +6289,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6303,12 +6299,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6323,6 +6314,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6340,10 +6351,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124133343</v>
+        <v>124126865</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6356,27 +6367,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6385,13 +6396,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436623</v>
+        <v>436624</v>
       </c>
       <c r="R47" t="n">
-        <v>7027816</v>
+        <v>7027776</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6420,7 +6431,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6430,12 +6441,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6454,22 +6460,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6487,10 +6493,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124126865</v>
+        <v>124132300</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6499,31 +6505,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6532,10 +6547,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436624</v>
+        <v>436689</v>
       </c>
       <c r="R48" t="n">
-        <v>7027776</v>
+        <v>7027839</v>
       </c>
       <c r="S48" t="n">
         <v>11</v>
@@ -6567,7 +6582,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6577,7 +6592,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6592,26 +6612,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138449</v>
+        <v>124126979</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6663,19 +6663,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436602</v>
+        <v>436580</v>
       </c>
       <c r="R49" t="n">
-        <v>7027958</v>
+        <v>7027758</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6702,14 +6707,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6720,23 +6735,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124126979</v>
+        <v>124138449</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6770,24 +6810,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436580</v>
+        <v>436602</v>
       </c>
       <c r="R50" t="n">
-        <v>7027758</v>
+        <v>7027958</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6814,24 +6849,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6842,41 +6867,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138425</v>
+        <v>124130402</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436739</v>
+        <v>436671</v>
       </c>
       <c r="R2" t="n">
-        <v>7028034</v>
+        <v>7027849</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +753,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +776,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124133243</v>
+        <v>124131819</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,31 +829,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,13 +862,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436634</v>
+        <v>436725</v>
       </c>
       <c r="R3" t="n">
-        <v>7027830</v>
+        <v>7027833</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +936,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138426</v>
+        <v>124131109</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,37 +975,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436760</v>
+        <v>436775</v>
       </c>
       <c r="R4" t="n">
-        <v>7028081</v>
+        <v>7027895</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,11 +1032,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,26 +1055,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124130043</v>
+        <v>124138432</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,60 +1108,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436564</v>
+        <v>436583</v>
       </c>
       <c r="R5" t="n">
-        <v>7027844</v>
+        <v>7028008</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,21 +1169,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1136,31 +1182,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124134307</v>
+        <v>124138466</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,37 +1214,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436504</v>
+        <v>436589</v>
       </c>
       <c r="R6" t="n">
-        <v>7027727</v>
+        <v>7027985</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,21 +1271,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1253,48 +1284,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124127075</v>
+        <v>124132562</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1328,24 +1334,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436458</v>
+        <v>436679</v>
       </c>
       <c r="R7" t="n">
-        <v>7027708</v>
+        <v>7027841</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,7 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,12 +1419,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,7 +1442,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124129449</v>
+        <v>124134307</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1472,17 +1478,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436417</v>
+        <v>436504</v>
       </c>
       <c r="R8" t="n">
-        <v>7027793</v>
+        <v>7027727</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1521,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138423</v>
+        <v>124138425</v>
       </c>
       <c r="B9" t="n">
         <v>91012</v>
@@ -1613,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436415</v>
+        <v>436739</v>
       </c>
       <c r="R9" t="n">
-        <v>7027827</v>
+        <v>7028034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1675,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124129618</v>
+        <v>124134147</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,21 +1697,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1720,13 +1726,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436474</v>
+        <v>436555</v>
       </c>
       <c r="R10" t="n">
-        <v>7027820</v>
+        <v>7027775</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1755,7 +1761,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1765,7 +1771,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,10 +1823,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124134147</v>
+        <v>124130731</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,27 +1839,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1862,10 +1877,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436555</v>
+        <v>436707</v>
       </c>
       <c r="R11" t="n">
-        <v>7027775</v>
+        <v>7027946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1897,7 +1912,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1907,7 +1922,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1922,26 +1937,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1959,10 +1954,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138453</v>
+        <v>124134617</v>
       </c>
       <c r="B12" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,38 +1966,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436490</v>
+        <v>436450</v>
       </c>
       <c r="R12" t="n">
-        <v>7027974</v>
+        <v>7027766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2032,11 +2027,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2045,16 +2055,41 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2163,10 +2198,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138434</v>
+        <v>124130826</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2179,37 +2214,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436588</v>
+        <v>436743</v>
       </c>
       <c r="R14" t="n">
-        <v>7027994</v>
+        <v>7027889</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2236,11 +2276,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2249,26 +2299,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138476</v>
+        <v>124138423</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2281,21 +2356,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2305,10 +2380,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436556</v>
+        <v>436415</v>
       </c>
       <c r="R15" t="n">
-        <v>7027990</v>
+        <v>7027827</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2367,10 +2442,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124126749</v>
+        <v>124129722</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2383,51 +2458,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436643</v>
+        <v>436509</v>
       </c>
       <c r="R16" t="n">
-        <v>7027739</v>
+        <v>7027814</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2456,7 +2517,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2466,12 +2527,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,6 +2542,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2503,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138481</v>
+        <v>124138462</v>
       </c>
       <c r="B17" t="n">
-        <v>88359</v>
+        <v>91457</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,25 +2591,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,10 +2619,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436391</v>
+        <v>436591</v>
       </c>
       <c r="R17" t="n">
-        <v>7027787</v>
+        <v>7028013</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2605,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124132562</v>
+        <v>124133534</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2621,21 +2697,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2645,13 +2721,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436679</v>
+        <v>436627</v>
       </c>
       <c r="R18" t="n">
-        <v>7027841</v>
+        <v>7027780</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2680,7 +2756,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2690,12 +2766,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2714,22 +2790,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2747,10 +2823,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124129722</v>
+        <v>124138459</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2763,37 +2839,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436509</v>
+        <v>436448</v>
       </c>
       <c r="R19" t="n">
-        <v>7027814</v>
+        <v>7027953</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2820,19 +2896,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:42</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2843,51 +2914,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124130607</v>
+        <v>124134174</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2896,41 +2942,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436700</v>
+        <v>436557</v>
       </c>
       <c r="R20" t="n">
-        <v>7027918</v>
+        <v>7027773</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2959,7 +3010,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2969,7 +3020,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,22 +3039,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3021,10 +3072,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124134174</v>
+        <v>124131669</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3033,31 +3084,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3066,13 +3117,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436557</v>
+        <v>436701</v>
       </c>
       <c r="R21" t="n">
-        <v>7027773</v>
+        <v>7027783</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3101,7 +3152,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3111,7 +3162,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3163,10 +3214,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124131523</v>
+        <v>124130043</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3175,41 +3226,60 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436749</v>
+        <v>436564</v>
       </c>
       <c r="R22" t="n">
-        <v>7027816</v>
+        <v>7027844</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3238,7 +3308,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3248,7 +3318,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3263,26 +3333,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3300,10 +3350,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124130109</v>
+        <v>124129449</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3316,47 +3366,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436613</v>
+        <v>436417</v>
       </c>
       <c r="R23" t="n">
-        <v>7027858</v>
+        <v>7027793</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3385,7 +3425,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3395,12 +3435,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3429,12 +3464,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3452,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124130826</v>
+        <v>124138428</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3468,42 +3503,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436743</v>
+        <v>436678</v>
       </c>
       <c r="R24" t="n">
-        <v>7027889</v>
+        <v>7028031</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3530,21 +3560,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3553,51 +3573,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124130487</v>
+        <v>124138481</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>88359</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3606,60 +3601,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436684</v>
+        <v>436391</v>
       </c>
       <c r="R25" t="n">
-        <v>7027902</v>
+        <v>7027787</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3686,21 +3662,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3709,31 +3675,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138432</v>
+        <v>124133629</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3746,37 +3707,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436583</v>
+        <v>436623</v>
       </c>
       <c r="R26" t="n">
-        <v>7028008</v>
+        <v>7027760</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3803,11 +3769,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3816,26 +3797,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138478</v>
+        <v>124138426</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3848,21 +3854,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3872,10 +3878,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436440</v>
+        <v>436760</v>
       </c>
       <c r="R27" t="n">
-        <v>7027952</v>
+        <v>7028081</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3934,10 +3940,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138436</v>
+        <v>124129992</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3950,37 +3956,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436408</v>
+        <v>436580</v>
       </c>
       <c r="R28" t="n">
-        <v>7027885</v>
+        <v>7027853</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4007,11 +4013,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4020,26 +4036,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124133629</v>
+        <v>124131523</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4052,42 +4093,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436623</v>
+        <v>436749</v>
       </c>
       <c r="R29" t="n">
-        <v>7027760</v>
+        <v>7027816</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4116,7 +4152,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4126,12 +4162,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4150,22 +4181,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Dead branch  # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4183,10 +4214,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138462</v>
+        <v>124133243</v>
       </c>
       <c r="B30" t="n">
-        <v>91457</v>
+        <v>79920</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4195,41 +4226,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436591</v>
+        <v>436634</v>
       </c>
       <c r="R30" t="n">
-        <v>7028013</v>
+        <v>7027830</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4256,11 +4292,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4269,26 +4315,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138474</v>
+        <v>124130607</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4301,37 +4372,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436493</v>
+        <v>436700</v>
       </c>
       <c r="R31" t="n">
-        <v>7027911</v>
+        <v>7027918</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4358,11 +4429,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4371,26 +4452,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124131109</v>
+        <v>124138474</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4403,37 +4509,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436775</v>
+        <v>436493</v>
       </c>
       <c r="R32" t="n">
-        <v>7027895</v>
+        <v>7027911</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4460,21 +4566,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4483,51 +4579,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124134617</v>
+        <v>124126749</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4540,37 +4611,51 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436450</v>
+        <v>436643</v>
       </c>
       <c r="R33" t="n">
-        <v>7027766</v>
+        <v>7027739</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4599,7 +4684,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4609,12 +4694,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>I flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4629,26 +4714,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4666,10 +4731,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124130731</v>
+        <v>124138436</v>
       </c>
       <c r="B34" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4682,48 +4747,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436707</v>
+        <v>436408</v>
       </c>
       <c r="R34" t="n">
-        <v>7027946</v>
+        <v>7027885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4753,21 +4804,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4776,31 +4817,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138431</v>
+        <v>124138478</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4813,21 +4849,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4837,10 +4873,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436653</v>
+        <v>436440</v>
       </c>
       <c r="R35" t="n">
-        <v>7028028</v>
+        <v>7027952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4899,10 +4935,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124129992</v>
+        <v>124138476</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4915,37 +4951,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436580</v>
+        <v>436556</v>
       </c>
       <c r="R36" t="n">
-        <v>7027853</v>
+        <v>7027990</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4972,21 +5008,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4995,51 +5021,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124130402</v>
+        <v>124127075</v>
       </c>
       <c r="B37" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5048,25 +5049,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5077,17 +5078,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436671</v>
+        <v>436458</v>
       </c>
       <c r="R37" t="n">
-        <v>7027849</v>
+        <v>7027708</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5116,7 +5117,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5126,7 +5127,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5145,22 +5146,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5178,10 +5179,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138466</v>
+        <v>124138453</v>
       </c>
       <c r="B38" t="n">
-        <v>91026</v>
+        <v>91705</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5190,25 +5191,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>67</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5218,10 +5219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436589</v>
+        <v>436490</v>
       </c>
       <c r="R38" t="n">
-        <v>7027985</v>
+        <v>7027974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5280,7 +5281,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138428</v>
+        <v>124138434</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -5320,10 +5321,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436678</v>
+        <v>436588</v>
       </c>
       <c r="R39" t="n">
-        <v>7028031</v>
+        <v>7027994</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5382,7 +5383,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124131819</v>
+        <v>124129618</v>
       </c>
       <c r="B40" t="n">
         <v>79891</v>
@@ -5427,13 +5428,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436725</v>
+        <v>436474</v>
       </c>
       <c r="R40" t="n">
-        <v>7027833</v>
+        <v>7027820</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5462,7 +5463,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5472,7 +5473,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5524,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124131669</v>
+        <v>124130109</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5540,27 +5541,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5569,13 +5575,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436701</v>
+        <v>436613</v>
       </c>
       <c r="R41" t="n">
-        <v>7027783</v>
+        <v>7027858</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5604,7 +5610,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5614,7 +5620,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5633,22 +5644,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5666,10 +5677,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138459</v>
+        <v>124138431</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5682,21 +5693,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5706,10 +5717,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436448</v>
+        <v>436653</v>
       </c>
       <c r="R42" t="n">
-        <v>7027953</v>
+        <v>7028028</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5742,11 +5753,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5920,10 +5926,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124133534</v>
+        <v>124130487</v>
       </c>
       <c r="B44" t="n">
-        <v>79892</v>
+        <v>57883</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5932,41 +5938,60 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436627</v>
+        <v>436684</v>
       </c>
       <c r="R44" t="n">
-        <v>7027780</v>
+        <v>7027902</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5995,7 +6020,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6005,12 +6030,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,26 +6045,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124133343</v>
+        <v>124126865</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6078,27 +6078,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6107,13 +6107,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436623</v>
+        <v>436624</v>
       </c>
       <c r="R45" t="n">
-        <v>7027816</v>
+        <v>7027776</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6152,12 +6152,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6176,22 +6171,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6209,10 +6204,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124133039</v>
+        <v>124132300</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6221,31 +6216,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6254,13 +6258,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436650</v>
+        <v>436689</v>
       </c>
       <c r="R46" t="n">
-        <v>7027809</v>
+        <v>7027839</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6289,7 +6293,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6299,7 +6303,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6314,26 +6323,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6351,10 +6340,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124126865</v>
+        <v>124133039</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6367,27 +6356,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6396,13 +6385,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436624</v>
+        <v>436650</v>
       </c>
       <c r="R47" t="n">
-        <v>7027776</v>
+        <v>7027809</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6431,7 +6420,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6441,7 +6430,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6470,12 +6459,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6493,10 +6482,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124132300</v>
+        <v>124133343</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6505,40 +6494,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6547,13 +6527,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436689</v>
+        <v>436623</v>
       </c>
       <c r="R48" t="n">
-        <v>7027839</v>
+        <v>7027816</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6582,7 +6562,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6592,12 +6572,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 100 plantor och 4 vinterståndare inom ca 1,5 m2 intill ett fuktstråk.</t>
+          <t>Växer mestadels långt upp på stammen på en högväxt gammal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6612,6 +6592,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124126979</v>
+        <v>124138449</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6663,24 +6663,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436580</v>
+        <v>436602</v>
       </c>
       <c r="R49" t="n">
-        <v>7027758</v>
+        <v>7027958</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6707,24 +6702,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6735,48 +6720,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138449</v>
+        <v>124134565</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6810,16 +6770,21 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436602</v>
+        <v>436416</v>
       </c>
       <c r="R50" t="n">
-        <v>7027958</v>
+        <v>7027743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6849,14 +6814,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6867,23 +6842,48 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124134565</v>
+        <v>124126979</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R51" t="n">
-        <v>7027743</v>
+        <v>7027758</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -6629,7 +6629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138449</v>
+        <v>124126979</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6663,19 +6663,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436602</v>
+        <v>436580</v>
       </c>
       <c r="R49" t="n">
-        <v>7027958</v>
+        <v>7027758</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6702,14 +6707,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6720,23 +6735,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124134565</v>
+        <v>124138449</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6770,21 +6810,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436416</v>
+        <v>436602</v>
       </c>
       <c r="R50" t="n">
-        <v>7027743</v>
+        <v>7027958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6814,24 +6849,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6842,48 +6867,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124126979</v>
+        <v>124134565</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436580</v>
+        <v>436416</v>
       </c>
       <c r="R51" t="n">
-        <v>7027758</v>
+        <v>7027743</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -6629,7 +6629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124126979</v>
+        <v>124134565</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6670,17 +6670,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436580</v>
+        <v>436416</v>
       </c>
       <c r="R49" t="n">
-        <v>7027758</v>
+        <v>7027743</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124134565</v>
+        <v>124126979</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R51" t="n">
-        <v>7027743</v>
+        <v>7027758</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -6629,7 +6629,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124134565</v>
+        <v>124138449</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6663,21 +6663,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Bleckåsen SV, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436416</v>
+        <v>436602</v>
       </c>
       <c r="R49" t="n">
-        <v>7027743</v>
+        <v>7027958</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6707,24 +6702,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6735,48 +6720,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138449</v>
+        <v>124126979</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6810,19 +6770,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bleckåsen SV, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436602</v>
+        <v>436580</v>
       </c>
       <c r="R50" t="n">
-        <v>7027958</v>
+        <v>7027758</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6849,14 +6814,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6867,23 +6842,48 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124126979</v>
+        <v>124134565</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436580</v>
+        <v>436416</v>
       </c>
       <c r="R51" t="n">
-        <v>7027758</v>
+        <v>7027743</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -6736,7 +6736,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124126979</v>
+        <v>124134565</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6777,17 +6777,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436580</v>
+        <v>436416</v>
       </c>
       <c r="R50" t="n">
-        <v>7027758</v>
+        <v>7027743</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124134565</v>
+        <v>124126979</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R51" t="n">
-        <v>7027743</v>
+        <v>7027758</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -6632,7 +6632,7 @@
         <v>124138449</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124134565</v>
+        <v>124126979</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6777,17 +6777,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R50" t="n">
-        <v>7027743</v>
+        <v>7027758</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6883,10 +6883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124126979</v>
+        <v>124134565</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436580</v>
+        <v>436416</v>
       </c>
       <c r="R51" t="n">
-        <v>7027758</v>
+        <v>7027743</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 22083-2021 artfynd.xlsx
+++ b/artfynd/A 22083-2021 artfynd.xlsx
@@ -6736,7 +6736,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124126979</v>
+        <v>124134565</v>
       </c>
       <c r="B50" t="n">
         <v>57635</v>
@@ -6777,17 +6777,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Getbackflon, Getbackflon, Jmt</t>
+          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436580</v>
+        <v>436416</v>
       </c>
       <c r="R50" t="n">
-        <v>7027758</v>
+        <v>7027743</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
+          <t>Ringhack, äldre, på en stående död gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124134565</v>
+        <v>124126979</v>
       </c>
       <c r="B51" t="n">
         <v>57635</v>
@@ -6924,17 +6924,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bäckdalsbäcken, Bäckdalsbäcken, Jmt</t>
+          <t>Getbackflon, Getbackflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436416</v>
+        <v>436580</v>
       </c>
       <c r="R51" t="n">
-        <v>7027743</v>
+        <v>7027758</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran.</t>
+          <t>Ringhack, äldre, på en nu död liggande gran som knäckts i stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
